--- a/inputs/en/LiST countries/SYR_databook.xlsx
+++ b/inputs/en/LiST countries/SYR_databook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F69DBAC4-7AE9-4B8A-A114-9CD5B8FDF038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D50A73-EB3F-4CD3-9693-E0C537FBBABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -9360,7 +9360,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="45">
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9368,7 +9368,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="45">
-        <v>0.77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11459,19 +11459,19 @@
       </c>
       <c r="D10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="E10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="F10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="G10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="H10" s="61">
         <v>0</v>
@@ -11805,19 +11805,19 @@
       </c>
       <c r="H18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="I18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="J18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="K18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="L18" s="61">
         <v>0</v>
@@ -20584,12 +20584,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="riIqDHxQDNIc95k8WEEMlpv2yK5yRhEl3GZr9d21PG7QnhNwxgtjaWmZN+9widROwyhXiwQ4XZiTM/cZ2Cl95g==" saltValue="b1Xx0XPjIcbtdUQJGdoNkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -20599,36 +20623,12 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -30088,13 +30088,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!$E$4),0.64, (0.64*SUM('Nutritional status distribution'!$E$4:$E$5)/(1-0.64*SUM('Nutritional status distribution'!$E$4:$E$5)))
-/ (SUM('Nutritional status distribution'!$E$4:$E$5)/(1-SUM('Nutritional status distribution'!$E$4:$E$5))))</f>
-        <v>0.6315408620528945</v>
+        <v>0.64</v>
       </c>
       <c r="F6" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!$F$4),0.64, (0.64*SUM('Nutritional status distribution'!$F$4:$F$5)/(1-0.64*SUM('Nutritional status distribution'!$F$4:$F$5)))/ (SUM('Nutritional status distribution'!$F$4:$F$5)/(1-SUM('Nutritional status distribution'!$F$4:$F$5))))</f>
-        <v>0.62105212099654195</v>
+        <v>0.64</v>
       </c>
       <c r="G6" s="90">
         <v>1</v>
@@ -30111,12 +30108,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!$E$4),0.88, (0.88*SUM('Nutritional status distribution'!$E$4:$E$5)/(1-0.88*SUM('Nutritional status distribution'!$E$4:$E$5)))/ (SUM('Nutritional status distribution'!$E$4:$E$5)/(1-SUM('Nutritional status distribution'!$E$4:$E$5))))</f>
-        <v>0.87608842789084607</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!$F$4),0.88, (0.88*SUM('Nutritional status distribution'!$F$4:$F$5)/(1-0.88*SUM('Nutritional status distribution'!$F$4:$F$5)))/ (SUM('Nutritional status distribution'!$F$4:$F$5)/(1-SUM('Nutritional status distribution'!$F$4:$F$5))))</f>
-        <v>0.87114069606187938</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="90">
         <v>1</v>
@@ -30133,12 +30128,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!$E$4),0.88, (0.88*SUM('Nutritional status distribution'!$E$4:$E$5)/(1-0.88*SUM('Nutritional status distribution'!$E$4:$E$5)))/ (SUM('Nutritional status distribution'!$E$4:$E$5)/(1-SUM('Nutritional status distribution'!$E$4:$E$5))))</f>
-        <v>0.87608842789084607</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!$F$4),0.88, (0.88*SUM('Nutritional status distribution'!$F$4:$F$5)/(1-0.88*SUM('Nutritional status distribution'!$F$4:$F$5)))/ (SUM('Nutritional status distribution'!$F$4:$F$5)/(1-SUM('Nutritional status distribution'!$F$4:$F$5))))</f>
-        <v>0.87114069606187938</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="90">
         <v>1</v>
@@ -30416,12 +30409,10 @@
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.44, (0.44*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.44*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
-        <v>0.43101936672301089</v>
+        <v>0.44</v>
       </c>
       <c r="F29" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.44, (0.44*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.44*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
-        <v>0.42006419640801851</v>
+        <v>0.44</v>
       </c>
       <c r="G29" s="90">
         <f>IF(G6=1,1,G6*0.9)</f>
@@ -30441,12 +30432,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.85, (0.85*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.85*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
-        <v>0.84528246350008318</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.85, (0.85*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.85*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
-        <v>0.83933025136621475</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="90">
         <f>IF(G7=1,1,G7*0.9)</f>
@@ -30466,12 +30455,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.85, (0.85*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.85*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
-        <v>0.84528246350008318</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.85, (0.85*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.85*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
-        <v>0.83933025136621475</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="90">
         <f>IF(G8=1,1,G8*0.9)</f>
@@ -30791,12 +30778,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.92, (0.92*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.92*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
-        <v>0.91726970741774339</v>
+        <v>0.92</v>
       </c>
       <c r="F52" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.92, (0.92*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.92*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
-        <v>0.91380454292294566</v>
+        <v>0.92</v>
       </c>
       <c r="G52" s="90">
         <f>IF(G6=1,1,G6*1.1)</f>
@@ -30816,12 +30801,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.91, (0.91*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.91*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
-        <v>0.90696293421596463</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.91, (0.91*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.91*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
-        <v>0.90311166887211425</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="90">
         <f>IF(G7=1,1,G7*1.1)</f>
@@ -30841,12 +30824,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.91, (0.91*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.91*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
-        <v>0.90696293421596463</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.91, (0.91*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.91*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
-        <v>0.90311166887211425</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="90">
         <f>IF(G8=1,1,G8*1.1)</f>
@@ -40720,177 +40701,4 @@
   <sheetProtection algorithmName="SHA-512" hashValue="tS5A5il384gB8zsJjwidwZIpdVsJo/ah59cRAmnHpig36ZssdSIeiIXxiNqdW+7yhHG743nXUgYflxFLjdX6Kg==" saltValue="H9BMcvjdiLgSEjFGZvTrQw==" spinCount="100000" sheet="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="107b52809c0cc4b5077f1ac81d3c69cc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b7e1b740270cfb0676be859a78f3d0" ns2:_="">
-    <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="12" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CC7E22F-2F8C-4404-8F70-FA6A3AE60F34}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA28C382-8B46-4FC7-AB7D-052AD8E8361F}"/>
 </file>
--- a/inputs/en/LiST countries/SYR_databook.xlsx
+++ b/inputs/en/LiST countries/SYR_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D50A73-EB3F-4CD3-9693-E0C537FBBABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C298DC56-14C2-4F49-B4C6-7AD58CACA546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Causes of death" sheetId="3" r:id="rId3"/>
     <sheet name="Nutritional status distribution" sheetId="4" r:id="rId4"/>
     <sheet name="Breastfeeding distribution" sheetId="5" r:id="rId5"/>
-    <sheet name="Time trends" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Time trends" sheetId="6" r:id="rId6"/>
     <sheet name="Economic loss" sheetId="7" r:id="rId7"/>
     <sheet name="IYCF packages" sheetId="8" r:id="rId8"/>
     <sheet name="Treatment of SAM" sheetId="9" r:id="rId9"/>
@@ -678,8 +678,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -692,8 +691,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -834,35 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -876,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -890,7 +860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
       <text>
         <r>
           <rPr>
@@ -904,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
+    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
       <text>
         <r>
           <rPr>
@@ -917,7 +887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
       <text>
         <r>
           <rPr>
@@ -930,7 +900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
       <text>
         <r>
           <rPr>
@@ -943,7 +913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
       <text>
         <r>
           <rPr>
@@ -956,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
       <text>
         <r>
           <rPr>
@@ -969,35 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1011,7 +953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1025,7 +967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1561,8 +1503,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -2134,8 +2075,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Peña‐Rosas et al 2019, anemia RR 0.72 (0.54-0.97)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2161,8 +2101,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Larson et al 2021, RR 0.80 (0.70-0.92)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2188,8 +2127,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -2652,7 +2590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2661,12 +2599,37 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2680,7 +2643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2694,7 +2657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2708,7 +2671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2722,7 +2685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2736,7 +2699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2750,7 +2713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2764,7 +2727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2778,7 +2741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2792,7 +2755,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2806,7 +2769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2820,7 +2783,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2834,7 +2797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2848,7 +2811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -2862,7 +2825,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -2876,7 +2839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -2890,7 +2853,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -2903,7 +2866,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -2916,7 +2879,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -2929,7 +2892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
       <text>
         <r>
           <rPr>
@@ -2942,7 +2905,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
       <text>
         <r>
           <rPr>
@@ -2955,7 +2918,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -2968,7 +2931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -2981,7 +2944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -2994,7 +2957,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -3007,7 +2970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -3020,7 +2983,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -3033,7 +2996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
       <text>
         <r>
           <rPr>
@@ -3046,7 +3009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -3060,7 +3023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -3074,7 +3037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -3088,7 +3051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -3102,7 +3065,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -3116,7 +3079,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -3130,7 +3093,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -3144,7 +3107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -3158,7 +3121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -3172,7 +3135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -3186,7 +3149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -3200,7 +3163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -3214,7 +3177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -3228,7 +3191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -3241,7 +3204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -3254,7 +3217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -3267,7 +3230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -3280,7 +3243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -3290,6 +3253,32 @@
           </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Wessells et al 2022, iron deficiency anemia), PR 0.36 (0.30-0.44) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -6929,9 +6918,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6943,9 +6931,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6957,9 +6944,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6971,9 +6957,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7106,68 +7091,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -7180,7 +7109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -7193,7 +7122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -7206,6 +7135,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A89" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
       <text>
         <r>
@@ -7227,9 +7208,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7241,9 +7221,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7255,9 +7234,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7269,9 +7247,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7358,7 +7335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="341">
   <si>
     <t>Baseline year data</t>
   </si>
@@ -9787,7 +9764,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="45">
-        <v>0.12637916779176001</v>
+        <v>0</v>
       </c>
       <c r="C2" s="98">
         <v>0.95</v>
@@ -9810,7 +9787,7 @@
         <v>168</v>
       </c>
       <c r="B3" s="45">
-        <v>0</v>
+        <v>0.2066742856206</v>
       </c>
       <c r="C3" s="98">
         <v>0.95</v>
@@ -9862,7 +9839,7 @@
         <v>0.95</v>
       </c>
       <c r="D5" s="56">
-        <v>1.270477719427328</v>
+        <v>1.347849812540453</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>167</v>
@@ -10109,7 +10086,7 @@
         <v>181</v>
       </c>
       <c r="B16" s="45">
-        <v>0.2066742856206</v>
+        <v>0.95</v>
       </c>
       <c r="C16" s="98">
         <v>0.95</v>
@@ -10132,7 +10109,7 @@
         <v>182</v>
       </c>
       <c r="B17" s="98">
-        <v>0.95</v>
+        <v>0.32122916666666701</v>
       </c>
       <c r="C17" s="98">
         <v>0.95</v>
@@ -10155,7 +10132,7 @@
         <v>148</v>
       </c>
       <c r="B18" s="98">
-        <v>0</v>
+        <v>0.11733278925379</v>
       </c>
       <c r="C18" s="98">
         <v>0.95</v>
@@ -10178,7 +10155,7 @@
         <v>151</v>
       </c>
       <c r="B19" s="98">
-        <v>0</v>
+        <v>0.89972340000000006</v>
       </c>
       <c r="C19" s="98">
         <v>0.95</v>
@@ -10224,7 +10201,7 @@
         <v>183</v>
       </c>
       <c r="B21" s="45">
-        <v>0.12046129999999999</v>
+        <v>0.80314839999999998</v>
       </c>
       <c r="C21" s="98">
         <v>0.95</v>
@@ -10270,7 +10247,7 @@
         <v>185</v>
       </c>
       <c r="B23" s="98">
-        <v>5.8989100000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C23" s="98">
         <v>0.95</v>
@@ -10293,7 +10270,7 @@
         <v>186</v>
       </c>
       <c r="B24" s="45">
-        <v>0.69723745018169003</v>
+        <v>0.88910919143547995</v>
       </c>
       <c r="C24" s="98">
         <v>0.95</v>
@@ -10362,7 +10339,7 @@
         <v>189</v>
       </c>
       <c r="B27" s="45">
-        <v>0.16203755015136001</v>
+        <v>0</v>
       </c>
       <c r="C27" s="98">
         <v>0.95</v>
@@ -10385,7 +10362,7 @@
         <v>190</v>
       </c>
       <c r="B28" s="45">
-        <v>0.45581739999999998</v>
+        <v>0.69723745018169003</v>
       </c>
       <c r="C28" s="98">
         <v>0.95</v>
@@ -10477,7 +10454,7 @@
         <v>193</v>
       </c>
       <c r="B32" s="45">
-        <v>7.7588900000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C32" s="98">
         <v>0.95</v>
@@ -10523,7 +10500,7 @@
         <v>195</v>
       </c>
       <c r="B34" s="45">
-        <v>0.89972340000000006</v>
+        <v>0</v>
       </c>
       <c r="C34" s="98">
         <v>0.95</v>
@@ -10569,7 +10546,7 @@
         <v>197</v>
       </c>
       <c r="B36" s="45">
-        <v>0</v>
+        <v>0.23215369999999999</v>
       </c>
       <c r="C36" s="98">
         <v>0.95</v>
@@ -10615,7 +10592,7 @@
         <v>199</v>
       </c>
       <c r="B38" s="45">
-        <v>0</v>
+        <v>0.45581739999999998</v>
       </c>
       <c r="C38" s="98">
         <v>0.95</v>
@@ -10638,7 +10615,7 @@
         <v>200</v>
       </c>
       <c r="B39" s="45">
-        <v>0.23215369999999999</v>
+        <v>0</v>
       </c>
       <c r="C39" s="98">
         <v>0.95</v>
@@ -15990,31 +15967,31 @@
         <v>2024</v>
       </c>
       <c r="B2" s="49">
-        <v>449674.5455999999</v>
+        <v>532402</v>
       </c>
       <c r="C2" s="49">
-        <v>1222000</v>
+        <v>1775399.5</v>
       </c>
       <c r="D2" s="49">
-        <v>2069000</v>
+        <v>2549319</v>
       </c>
       <c r="E2" s="49">
-        <v>785000</v>
+        <v>1464377</v>
       </c>
       <c r="F2" s="49">
-        <v>519000</v>
+        <v>1186209</v>
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G13" si="0">C2+D2+E2+F2</f>
-        <v>4595000</v>
+        <v>6975304.5</v>
       </c>
       <c r="H2" s="17">
         <f t="shared" ref="H2:H13" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
-        <v>516646.82740844635</v>
+        <v>611695.29584756587</v>
       </c>
       <c r="I2" s="17">
         <f t="shared" ref="I2:I13" si="2">G2-H2</f>
-        <v>4078353.1725915535</v>
+        <v>6363609.2041524341</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16023,31 +16000,31 @@
         <v>2025</v>
       </c>
       <c r="B3" s="49">
-        <v>467822.01299999998</v>
+        <v>573943</v>
       </c>
       <c r="C3" s="50">
-        <v>1231000</v>
+        <v>1795384.5</v>
       </c>
       <c r="D3" s="50">
-        <v>2158000</v>
+        <v>2780169</v>
       </c>
       <c r="E3" s="50">
-        <v>794000</v>
+        <v>1581613.5</v>
       </c>
       <c r="F3" s="50">
-        <v>542000</v>
+        <v>1231949</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="0"/>
-        <v>4725000</v>
+        <v>7389116</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>537497.08800124482</v>
+        <v>659423.20499291795</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="2"/>
-        <v>4187502.9119987553</v>
+        <v>6729692.7950070817</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16056,31 +16033,31 @@
         <v>2026</v>
       </c>
       <c r="B4" s="49">
-        <v>480535.56400000007</v>
+        <v>610419</v>
       </c>
       <c r="C4" s="50">
-        <v>1244000</v>
+        <v>1790412</v>
       </c>
       <c r="D4" s="50">
-        <v>2241000</v>
+        <v>2971406.5</v>
       </c>
       <c r="E4" s="50">
-        <v>801000</v>
+        <v>1709798</v>
       </c>
       <c r="F4" s="50">
-        <v>568000</v>
+        <v>1273598.5</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="0"/>
-        <v>4854000</v>
+        <v>7745215</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="1"/>
-        <v>552104.13181441266</v>
+        <v>701331.7583254294</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>4301895.8681855872</v>
+        <v>7043883.2416745704</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16089,31 +16066,31 @@
         <v>2027</v>
       </c>
       <c r="B5" s="49">
-        <v>490941.87699999998</v>
+        <v>639263</v>
       </c>
       <c r="C5" s="50">
-        <v>1250000</v>
+        <v>1755175</v>
       </c>
       <c r="D5" s="50">
-        <v>2302000</v>
+        <v>3125682</v>
       </c>
       <c r="E5" s="50">
-        <v>803000</v>
+        <v>1849299.5</v>
       </c>
       <c r="F5" s="50">
-        <v>598000</v>
+        <v>1310525</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="0"/>
-        <v>4953000</v>
+        <v>8040681.5</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="1"/>
-        <v>564060.3091188129</v>
+        <v>734471.63968092238</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>4388939.6908811871</v>
+        <v>7306209.860319078</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16122,31 +16099,31 @@
         <v>2028</v>
       </c>
       <c r="B6" s="49">
-        <v>499456.12500000012</v>
+        <v>665188</v>
       </c>
       <c r="C6" s="50">
-        <v>1251000</v>
+        <v>1678421.5</v>
       </c>
       <c r="D6" s="50">
-        <v>2347000</v>
+        <v>3250326.5</v>
       </c>
       <c r="E6" s="50">
-        <v>803000</v>
+        <v>2002848</v>
       </c>
       <c r="F6" s="50">
-        <v>630000</v>
+        <v>1342899</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="0"/>
-        <v>5031000</v>
+        <v>8274495</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>573842.62670830288</v>
+        <v>764257.77974960767</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>4457157.3732916974</v>
+        <v>7510237.2202503923</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16155,31 +16132,31 @@
         <v>2029</v>
       </c>
       <c r="B7" s="49">
-        <v>506833.04700000008</v>
+        <v>684175</v>
       </c>
       <c r="C7" s="50">
-        <v>1250000</v>
+        <v>1574473</v>
       </c>
       <c r="D7" s="50">
-        <v>2379000</v>
+        <v>3335087.5</v>
       </c>
       <c r="E7" s="50">
-        <v>799000</v>
+        <v>2170490.5</v>
       </c>
       <c r="F7" s="50">
-        <v>661000</v>
+        <v>1370461</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="0"/>
-        <v>5089000</v>
+        <v>8450512</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>582318.23064148566</v>
+        <v>786072.60873645917</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>4506681.7693585139</v>
+        <v>7664439.3912635408</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16188,31 +16165,31 @@
         <v>2030</v>
       </c>
       <c r="B8" s="49">
-        <v>513614.22399999999</v>
+        <v>699103</v>
       </c>
       <c r="C8" s="50">
-        <v>1247000</v>
+        <v>1465464.5</v>
       </c>
       <c r="D8" s="50">
-        <v>2404000</v>
+        <v>3371692</v>
       </c>
       <c r="E8" s="50">
-        <v>795000</v>
+        <v>2346187</v>
       </c>
       <c r="F8" s="50">
-        <v>687000</v>
+        <v>1392492.5</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
-        <v>5133000</v>
+        <v>8575836</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>590109.36228864267</v>
+        <v>803223.91052798601</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>4542890.6377113573</v>
+        <v>7772612.0894720145</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16221,31 +16198,31 @@
         <v>2031</v>
       </c>
       <c r="B9" s="49">
-        <v>522748.46377142862</v>
+        <v>706443</v>
       </c>
       <c r="C9" s="50">
-        <v>1250571.4285714291</v>
+        <v>1362082.5</v>
       </c>
       <c r="D9" s="50">
-        <v>2451857.1428571432</v>
+        <v>3363171</v>
       </c>
       <c r="E9" s="50">
-        <v>796428.57142857148</v>
+        <v>2525926.5</v>
       </c>
       <c r="F9" s="50">
-        <v>711000</v>
+        <v>1410994</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="0"/>
-        <v>5209857.1428571437</v>
+        <v>8662174</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>600604.01012867072</v>
+        <v>811657.09348282288</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>4609253.1327284733</v>
+        <v>7850516.9065171769</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16254,31 +16231,31 @@
         <v>2032</v>
       </c>
       <c r="B10" s="49">
-        <v>530595.09959591832</v>
+        <v>710855</v>
       </c>
       <c r="C10" s="50">
-        <v>1253367.3469387761</v>
+        <v>1271529</v>
       </c>
       <c r="D10" s="50">
-        <v>2493836.7346938769</v>
+        <v>3316385.5</v>
       </c>
       <c r="E10" s="50">
-        <v>796775.51020408166</v>
+        <v>2703312.5</v>
       </c>
       <c r="F10" s="50">
-        <v>735142.85714285716</v>
+        <v>1428747</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>5279122.448979592</v>
+        <v>8719974</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>609619.28471830289</v>
+        <v>816726.19473578501</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>4669503.1642612889</v>
+        <v>7903247.805264215</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16287,31 +16264,31 @@
         <v>2033</v>
       </c>
       <c r="B11" s="49">
-        <v>537746.46182390663</v>
+        <v>702271</v>
       </c>
       <c r="C11" s="50">
-        <v>1254705.539358601</v>
+        <v>1204044.5</v>
       </c>
       <c r="D11" s="50">
-        <v>2529956.2682215739</v>
+        <v>3240248</v>
       </c>
       <c r="E11" s="50">
-        <v>796172.01166180766</v>
+        <v>2868461.5</v>
       </c>
       <c r="F11" s="50">
-        <v>759020.40816326533</v>
+        <v>1449682.5</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="0"/>
-        <v>5339854.2274052482</v>
+        <v>8762436.5</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>617835.73513314442</v>
+        <v>806863.73663165409</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>4722018.4922721041</v>
+        <v>7955572.7633683458</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16320,31 +16297,31 @@
         <v>2034</v>
       </c>
       <c r="B12" s="49">
-        <v>544432.83108446468</v>
+        <v>694568</v>
       </c>
       <c r="C12" s="50">
-        <v>1255377.7592669721</v>
+        <v>1177233</v>
       </c>
       <c r="D12" s="50">
-        <v>2562521.449396085</v>
+        <v>3131602</v>
       </c>
       <c r="E12" s="50">
-        <v>795196.58475635166</v>
+        <v>3015146.5</v>
       </c>
       <c r="F12" s="50">
-        <v>782023.32361516042</v>
+        <v>1480634</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="0"/>
-        <v>5395119.1170345694</v>
+        <v>8804615.5</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" si="1"/>
-        <v>625517.93884947733</v>
+        <v>798013.49026910507</v>
       </c>
       <c r="I12" s="17">
         <f t="shared" si="2"/>
-        <v>4769601.1781850923</v>
+        <v>8006602.009730895</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16353,31 +16330,31 @@
         <v>2035</v>
       </c>
       <c r="B13" s="49">
-        <v>550858.07481081679</v>
+        <v>680805</v>
       </c>
       <c r="C13" s="50">
-        <v>1256003.153447968</v>
+        <v>1190252</v>
       </c>
       <c r="D13" s="50">
-        <v>2593310.2278812402</v>
+        <v>2993307</v>
       </c>
       <c r="E13" s="50">
-        <v>794081.81115011615</v>
+        <v>3139393</v>
       </c>
       <c r="F13" s="50">
-        <v>803740.94127446902</v>
+        <v>1526329</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="0"/>
-        <v>5447136.1337537933</v>
+        <v>8849281</v>
       </c>
       <c r="H13" s="17">
         <f t="shared" si="1"/>
-        <v>632900.12629821652</v>
+        <v>782200.69776128198</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>4814236.0074555771</v>
+        <v>8067080.3022387177</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16916,7 +16893,7 @@
         <v>145</v>
       </c>
       <c r="D5" s="88">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="88">
         <v>1</v>
@@ -16937,7 +16914,7 @@
         <v>146</v>
       </c>
       <c r="D6" s="88">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="88">
         <v>1</v>
@@ -16984,7 +16961,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="88">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="88">
         <v>1</v>
@@ -17005,7 +16982,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="88">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="88">
         <v>1</v>
@@ -18036,7 +18013,7 @@
         <v>145</v>
       </c>
       <c r="D58" s="88">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="88">
         <f t="shared" ref="E58:H60" si="1">IF(E5=1,1,E5*0.9)</f>
@@ -18061,7 +18038,7 @@
         <v>146</v>
       </c>
       <c r="D59" s="88">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="88">
         <f t="shared" si="1"/>
@@ -18118,7 +18095,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="88">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="88">
         <f t="shared" ref="F61:H63" si="3">IF(F8=1,1,F8*0.9)</f>
@@ -18143,7 +18120,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="88">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="88">
         <f t="shared" si="3"/>
@@ -19373,7 +19350,7 @@
         <v>145</v>
       </c>
       <c r="D111" s="88">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="88">
         <f t="shared" ref="E111:H113" si="11">IF(E5=1,1,E5*1.05)</f>
@@ -19398,7 +19375,7 @@
         <v>146</v>
       </c>
       <c r="D112" s="88">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="88">
         <f t="shared" si="11"/>
@@ -19455,7 +19432,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="88">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="88">
         <f t="shared" ref="F114:H116" si="13">IF(F8=1,1,F8*1.05)</f>
@@ -19480,7 +19457,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="88">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="88">
         <f t="shared" si="13"/>
@@ -20582,7 +20559,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="riIqDHxQDNIc95k8WEEMlpv2yK5yRhEl3GZr9d21PG7QnhNwxgtjaWmZN+9widROwyhXiwQ4XZiTM/cZ2Cl95g==" saltValue="b1Xx0XPjIcbtdUQJGdoNkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
@@ -21844,7 +21821,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OEa5xq8Dht0iRzVx1fQ1EOJdDm09uSIzQRujIfp/VJ8GNGNECqE8Uut2U6j1omy5Y9ajcKxMUHwzsTWrCb+nAw==" saltValue="Poj67khbkyqhF7WVYd6CsA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="a0aX2VfGYRJWLRZcCd5z7lhlUmGJO/EzN4cg0Snhkl/IJQUK1zIL/9W0H+8Dtzn8tPzB4mSWxW65xqA1yiTgOA==" saltValue="o1GVWZzk0+60bY16Wxar5Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -29979,7 +29956,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rzjjr+eUY+zLxtgvRuigrXBCYk8ZjZeKkvy/Wu7lqFGhk7GKsrVngS9i2Jt2gxX9Fn0pC2b9tyB7+BxRGGivEA==" saltValue="vsQDJsypwJz22iUc18xJ6w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1gEiboypgN1VYdmLYuHEsviiXDH91vsC32xKqzOEbclcsh2pOXs0vX071vry3NRJsC+T2/BNfpXbXWW7dldjVQ==" saltValue="XZihSWmo245BlR0GYalydw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -30088,10 +30065,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="90">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="90">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="90">
         <v>1</v>
@@ -30409,10 +30386,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <v>0.44</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="90">
-        <v>0.44</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="90">
         <f>IF(G6=1,1,G6*0.9)</f>
@@ -30778,10 +30757,12 @@
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <v>0.92</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="90">
-        <v>0.92</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="90">
         <f>IF(G6=1,1,G6*1.1)</f>
@@ -31043,7 +31024,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uxH3qxfpHv3MxEVFpMF959vuuHVMbjUY0YDJlIXIgHOAA25UaRTm/IIjRx7RzEUfWaTP3eP7cZpYIm+m6J8PbA==" saltValue="wm1A0TwV/0DyOIoqtNvfsQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z5W0iLQonUXgebQ0oBIAJiknKvZHIMnPuF1vh21+BfR+VnJC7YVzBoFQiTm+hEbHNMOFIRa563Ft7+Jm2vvcKg==" saltValue="MgosxU+mdCbdebb7wBaTKg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31864,7 +31845,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lEvf/7Nn9p0s2t120JFgJzNA1BIMAO9h8EmTziKGX5ZA7K3Y+rQ77oXfzNqKwsdbYQwCY96ujjsdxuDmqt1luA==" saltValue="pZcegXbvW/wKpwHEQP8pcw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LnjPs+tiryCjGlxIcCoc9VYZVK7anRAVHCvKud83EfjtgKW0vUQr2FSI3nvdju1neMs4gxoXRQGAXnwHTy0eGQ==" saltValue="uusuOaSrLiI1eiqZNmtU+w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31939,7 +31920,7 @@
         <v>170</v>
       </c>
       <c r="C3" s="90">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="90">
         <v>0.53</v>
@@ -32450,16 +32431,16 @@
         <v>1</v>
       </c>
       <c r="L14" s="90">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="M14" s="90">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="N14" s="90">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="O14" s="90">
-        <v>0.51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -32567,48 +32548,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="90">
-        <f t="shared" ref="E19:O19" si="0">0.72</f>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="90">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -32666,37 +32636,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="90">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -32757,53 +32727,53 @@
         <v>170</v>
       </c>
       <c r="C26" s="90">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="90">
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -32812,23 +32782,23 @@
         <v>175</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32844,19 +32814,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32865,23 +32835,23 @@
         <v>176</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32897,19 +32867,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32918,23 +32888,23 @@
         <v>177</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -32950,19 +32920,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32971,23 +32941,23 @@
         <v>178</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -33003,19 +32973,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -33024,39 +32994,39 @@
         <v>179</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33077,39 +33047,39 @@
         <v>180</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33130,39 +33100,39 @@
         <v>181</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33200,19 +33170,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33281,11 +33251,11 @@
         <v>188</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33298,35 +33268,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -33335,56 +33305,52 @@
         <v>189</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="90">
-        <f>M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="90">
-        <f>N32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="90">
-        <f>O32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -33392,11 +33358,11 @@
         <v>192</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33406,39 +33372,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -33453,55 +33419,55 @@
         <v>172</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="8">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -33510,45 +33476,45 @@
         <v>173</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="9">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="90">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -33556,55 +33522,55 @@
         <v>174</v>
       </c>
       <c r="C43" s="90">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="D43" s="90">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="90">
+        <f t="shared" ref="E43:O43" si="10">IF(E20=1,1,E20*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="F43" s="90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D43" s="90">
+      <c r="G43" s="90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
-      </c>
-      <c r="F43" s="90">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="G43" s="90">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
       <c r="H43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -33613,45 +33579,45 @@
         <v>182</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="90">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -33712,53 +33678,53 @@
         <v>170</v>
       </c>
       <c r="C49" s="90">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="90">
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="11">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33767,23 +33733,23 @@
         <v>175</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="12">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33799,19 +33765,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="13">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -33820,23 +33786,23 @@
         <v>176</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33852,19 +33818,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -33873,23 +33839,23 @@
         <v>177</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -33905,19 +33871,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -33926,23 +33892,23 @@
         <v>178</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -33958,19 +33924,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -33979,39 +33945,39 @@
         <v>179</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="14">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -34032,39 +33998,39 @@
         <v>180</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34085,39 +34051,39 @@
         <v>181</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
@@ -34156,19 +34122,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34237,11 +34203,11 @@
         <v>188</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="15">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34254,35 +34220,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="16">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
@@ -34291,56 +34257,52 @@
         <v>189</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="17">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="90">
-        <f>M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="90">
-        <f>N54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="90">
-        <f>O54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34348,11 +34310,11 @@
         <v>192</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34362,39 +34324,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="18">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -34409,55 +34371,55 @@
         <v>172</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="19">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -34466,45 +34428,45 @@
         <v>173</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="20">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="90">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -34512,55 +34474,55 @@
         <v>174</v>
       </c>
       <c r="C66" s="90">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="D66" s="90">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="E66" s="90">
+        <f t="shared" ref="E66:O66" si="21">IF(E20=1,1,E20*1.05)</f>
+        <v>1</v>
+      </c>
+      <c r="F66" s="90">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="D66" s="90">
+      <c r="G66" s="90">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="F66" s="90">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="G66" s="90">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
       <c r="H66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>
@@ -34569,51 +34531,49 @@
         <v>182</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="90">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="90">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.92,(0.92*'Nutritional status distribution'!O$14/(1-0.92*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
-        <v>0.89757246747925845</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QTNrTNcX0LQnvnw9OcFIuF8iiKsb7nBsadUCrO1kCxqB4CvEkER3v8YCwNBmR8txM/1IAuOQ/zC/vA8HLWjOhA==" saltValue="f5+QlQPEjGE24L/HhPaCMQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z+I5w7Zv8b/t9kdTHtfTBlYoSm79UCEUpz3ShmnqEGsFIWvoyqli8qZ/O3UtxFRtNUOisgC6wk7M7CD5q+6g2w==" saltValue="qncMJDCOHin5ZX0oUaABDg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34895,7 +34855,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZIjv20oIFeX8hEAP3JXu7+FjYQdIWvRgXIH4IkxRsMm14MAW5JMg2x9QOPJ7rc+IAMFEDvKO0XCydnz4Atw3VA==" saltValue="eIHIWivrA2mRyU/FI0KAAQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TSrwgMfue31l5YKH5YC63gNl/EJnr5ZJbUkDIAIpA9VCbqMkKC4yV7Qlzd02MRVNDQ406JZzgd4mO0azU8HKbQ==" saltValue="P3gP/2fV5vANzIL7NniDMg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -38623,7 +38583,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gIF3gzcRwMevsVP9JM+eFJliWIfkjL6RYnVy29HH1zFwKTB/eJc1NVFGROY84dwrfqcI+B8KpOZ1waT1qDgCXQ==" saltValue="0Itsi1W8Rg+oXl6coWpocw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ogxQtq/9g6OeNkiNBs6ghJq8+LdVqsoK1CbSDtbSeFSK0ebg4cqAnXfIn86tuaNowgHjhLbE7woQSAqVYa5K1w==" saltValue="QFHNUEWTAfsZg09RvHfUXA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39127,7 +39087,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SSCu+FR+SN+siPEoAiap+3g3Z0SGqFtJklZqGSbEJvGKfBY2J7BHBpfevFvAYPx8Hf15tBeGKZdJ4ehQEpyLRg==" saltValue="A0PmMaoo+OfazXy7x4UxVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bFi4UO/MYSy1ocOot5y7JdpTLSj3VYrhdtuVEmlekdzp7NtFBQZX4yNIi9A9S9nFic+mLseFiB4QMgSz7PmPmQ==" saltValue="0Yi1KsKDfpD+pl5y1FWoHw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40467,7 +40427,9 @@
         <v>78</v>
       </c>
       <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="D5" s="47" t="s">
+        <v>149</v>
+      </c>
       <c r="E5" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
@@ -40478,7 +40440,9 @@
         <v>79</v>
       </c>
       <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="47" t="s">
+        <v>149</v>
+      </c>
       <c r="E6" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
@@ -40701,4 +40665,177 @@
   <sheetProtection algorithmName="SHA-512" hashValue="tS5A5il384gB8zsJjwidwZIpdVsJo/ah59cRAmnHpig36ZssdSIeiIXxiNqdW+7yhHG743nXUgYflxFLjdX6Kg==" saltValue="H9BMcvjdiLgSEjFGZvTrQw==" spinCount="100000" sheet="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="107b52809c0cc4b5077f1ac81d3c69cc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b7e1b740270cfb0676be859a78f3d0" ns2:_="">
+    <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="12" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BBFB86B-E66E-4B6E-9AE6-00CA113D293A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B104FC5-BB31-438A-8118-F402856F2F34}"/>
 </file>
--- a/inputs/en/LiST countries/SYR_databook.xlsx
+++ b/inputs/en/LiST countries/SYR_databook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C298DC56-14C2-4F49-B4C6-7AD58CACA546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ABFB6A7-A3A8-4A14-A8FA-3AF536326565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Baseline year population inputs'!$C$47</definedName>
     <definedName name="U5_mortality">'Baseline year population inputs'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2088,7 +2088,8 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.</t>
+Insufficient published research on the intervention’s effect on the outcome.
+Thereofre, set effect of rice = effect of wheat</t>
         </r>
       </text>
     </comment>
@@ -7335,7 +7336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="341">
   <si>
     <t>Baseline year data</t>
   </si>
@@ -9379,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="45">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9387,7 +9388,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="45">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9395,7 +9396,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="45">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9404,7 +9405,7 @@
       </c>
       <c r="C20" s="46">
         <f>1-frac_rice-frac_wheat-frac_maize</f>
-        <v>0.20000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10634,7 +10635,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7vflRb+A4U2pEdxn7m/v0lFZNI78qfZXbnYBjV1V9XLM+tHWxQCvL8xYVSz8kIygwB6Bp0chVfPhUDXzL0eOkw==" saltValue="BwzbjGZ5GxwK0BvfdhnvSQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SwqShMKjZ/Tc3FrdHQz/MjdsWftRTk85s02s32k0tDk98bBhXaGhkqbuII/OivPUJtqXOhQ4ck/oX/RBAeMIgQ==" saltValue="RORLzDUZEp7fquGh4DZ5hw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10704,23 +10705,39 @@
       <c r="C5" s="47"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58"/>
+      <c r="A6" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>192</v>
+      </c>
       <c r="C6" s="58"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
+      <c r="A7" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>192</v>
+      </c>
       <c r="C7" s="58"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
+      <c r="A8" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>192</v>
+      </c>
       <c r="C8" s="58"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
+      <c r="A9" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>192</v>
+      </c>
       <c r="C9" s="58"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -12261,47 +12278,47 @@
       </c>
       <c r="E30" s="60">
         <f t="shared" ref="E30:O30" si="0">frac_maize</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="N30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12316,47 +12333,47 @@
       </c>
       <c r="E31" s="60">
         <f t="shared" ref="E31:O31" si="1">frac_rice</f>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="H31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="I31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="J31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="K31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="L31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="M31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="N31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="O31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12371,47 +12388,47 @@
       </c>
       <c r="E32" s="60">
         <f t="shared" ref="E32:O32" si="2">frac_wheat</f>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="F32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="G32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="H32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="I32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="J32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="K32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="L32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="M32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="N32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="O32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20561,6 +20578,42 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="B151:B153"/>
@@ -20570,42 +20623,6 @@
     <mergeCell ref="B134:B136"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -32431,16 +32448,20 @@
         <v>1</v>
       </c>
       <c r="L14" s="90">
-        <v>1</v>
+        <f>L8</f>
+        <v>0.51</v>
       </c>
       <c r="M14" s="90">
-        <v>1</v>
+        <f>M8</f>
+        <v>0.51</v>
       </c>
       <c r="N14" s="90">
-        <v>1</v>
+        <f>N8</f>
+        <v>0.51</v>
       </c>
       <c r="O14" s="90">
-        <v>1</v>
+        <f>O8</f>
+        <v>0.51</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -32592,37 +32613,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="90">
-        <v>1</v>
+        <f t="shared" ref="E20:O20" si="0">E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -32733,47 +32765,47 @@
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -32782,23 +32814,23 @@
         <v>175</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32814,19 +32846,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32835,23 +32867,23 @@
         <v>176</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32867,19 +32899,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32888,23 +32920,23 @@
         <v>177</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -32920,19 +32952,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32941,23 +32973,23 @@
         <v>178</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -32973,19 +33005,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32994,39 +33026,39 @@
         <v>179</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33047,39 +33079,39 @@
         <v>180</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33100,39 +33132,39 @@
         <v>181</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33170,19 +33202,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33251,11 +33283,11 @@
         <v>188</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33268,35 +33300,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -33305,39 +33337,39 @@
         <v>189</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
@@ -33358,11 +33390,11 @@
         <v>192</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33372,39 +33404,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -33419,55 +33451,55 @@
         <v>172</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="8">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -33476,11 +33508,11 @@
         <v>173</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="9">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
@@ -33522,56 +33554,56 @@
         <v>174</v>
       </c>
       <c r="C43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="10">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
+        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -33579,11 +33611,11 @@
         <v>182</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
@@ -33684,47 +33716,47 @@
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="11">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -33733,23 +33765,23 @@
         <v>175</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="12">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33765,19 +33797,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="13">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33786,23 +33818,23 @@
         <v>176</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33818,19 +33850,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33839,23 +33871,23 @@
         <v>177</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -33871,19 +33903,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33892,23 +33924,23 @@
         <v>178</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -33924,19 +33956,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33945,39 +33977,39 @@
         <v>179</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="14">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -33998,39 +34030,39 @@
         <v>180</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34051,39 +34083,39 @@
         <v>181</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
@@ -34122,19 +34154,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34203,11 +34235,11 @@
         <v>188</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="15">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34220,35 +34252,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="16">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34257,39 +34289,39 @@
         <v>189</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="17">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
@@ -34310,11 +34342,11 @@
         <v>192</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34324,39 +34356,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="18">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -34371,55 +34403,55 @@
         <v>172</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="19">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -34428,11 +34460,11 @@
         <v>173</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="20">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
@@ -34474,56 +34506,56 @@
         <v>174</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="21">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
+        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -34531,11 +34563,11 @@
         <v>182</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
@@ -40665,177 +40697,4 @@
   <sheetProtection algorithmName="SHA-512" hashValue="tS5A5il384gB8zsJjwidwZIpdVsJo/ah59cRAmnHpig36ZssdSIeiIXxiNqdW+7yhHG743nXUgYflxFLjdX6Kg==" saltValue="H9BMcvjdiLgSEjFGZvTrQw==" spinCount="100000" sheet="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="107b52809c0cc4b5077f1ac81d3c69cc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b7e1b740270cfb0676be859a78f3d0" ns2:_="">
-    <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="12" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BBFB86B-E66E-4B6E-9AE6-00CA113D293A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B104FC5-BB31-438A-8118-F402856F2F34}"/>
 </file>
--- a/inputs/en/LiST countries/SYR_databook.xlsx
+++ b/inputs/en/LiST countries/SYR_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ABFB6A7-A3A8-4A14-A8FA-3AF536326565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A4BE210-6C2D-491C-9C1C-AC4C08F612D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Baseline year population inputs'!$C$47</definedName>
     <definedName name="U5_mortality">'Baseline year population inputs'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -587,52 +587,167 @@
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Nick Scott</author>
     <author>Tharindu Wickramaarachchi</author>
   </authors>
   <commentList>
-    <comment ref="B56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-LiST 6.29
-Katz J, Lee AC, Kozuki N, et al. Mortality risk in preterm and small-for-gestational-age infants in low-income and middle-income countries: A pooled country analysis. Lancet 2013; 382(9890): 417–25</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-LiST 6.29
-Black RE, Victora CG, Walker SP, et al. Maternal and child undernutrition and overweight in low-income and middle-income countries. Lancet 2013; 382(9890): 427-51. http://www.ncbi.nlm.nih.gov/pubmed/23746772. (Supplementary material - Web Table 17.)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Spectrum LiST 6.29</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A220" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000004000000}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Heidkamp R, Guida R, Phillips E, Clermont A. The Lives Saved Tool (LiST) as a Model for Prevention of Anemia in Women of Reproductive Age. J Nutr. 2017;147(11):2156S-2162S</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D86" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D98" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A220" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1500-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -656,7 +771,21 @@
     <author>Tharindu Wickramaarachchi</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000001000000}">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Checkley et al. Int J Epidemiol 2008.
+The adjusted odds of stunting increased by 1.13 for every five episodes (95% CI 1.07-1.19)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -669,7 +798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000002000000}">
+    <comment ref="E6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -682,7 +811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000003000000}">
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -695,7 +824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000004000000}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -709,7 +838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000005000000}">
+    <comment ref="E7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000006000000}">
       <text>
         <r>
           <rPr>
@@ -723,7 +852,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000006000000}">
+    <comment ref="F7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000007000000}">
       <text>
         <r>
           <rPr>
@@ -736,7 +865,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000007000000}">
+    <comment ref="E8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000008000000}">
       <text>
         <r>
           <rPr>
@@ -749,7 +878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000008000000}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000009000000}">
       <text>
         <r>
           <rPr>
@@ -762,7 +891,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000009000000}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -780,7 +909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000A000000}">
+    <comment ref="C12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -793,7 +922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000B000000}">
+    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -806,7 +935,51 @@
         </r>
       </text>
     </comment>
-    <comment ref="A28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000C000000}">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Checkley et al. Int J Epidemiol 2008.
+The adjusted odds of stunting increased by 1.13 for every five episodes (95% CI 1.07-1.19)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
       <text>
         <r>
           <rPr>
@@ -819,7 +992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000D000000}">
+    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
       <text>
         <r>
           <rPr>
@@ -832,7 +1005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
       <text>
         <r>
           <rPr>
@@ -846,7 +1019,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
       <text>
         <r>
           <rPr>
@@ -860,7 +1033,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
       <text>
         <r>
           <rPr>
@@ -874,7 +1047,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
+    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
       <text>
         <r>
           <rPr>
@@ -887,7 +1060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
       <text>
         <r>
           <rPr>
@@ -900,7 +1073,37 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
       <text>
         <r>
           <rPr>
@@ -913,7 +1116,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Checkley et al. Int J Epidemiol 2008.
+The adjusted odds of stunting increased by 1.13 for every five episodes (95% CI 1.07-1.19)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -926,7 +1143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -939,7 +1156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -953,7 +1170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -967,7 +1184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -978,6 +1195,36 @@
           <t>Tharindu Wickramaarachchi:
 Dewey et al 2021, stunting, PR 0.88 (0.85-0.91)  
 Converted to OR is prev. data inputs are available else RR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000020000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000021000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
         </r>
       </text>
     </comment>
@@ -2062,11 +2309,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002B000000}">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -2079,21 +2326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.
-Thereofre, set effect of rice = effect of wheat</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002D000000}">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -2106,7 +2339,280 @@
         </r>
       </text>
     </comment>
-    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002E000000}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000030000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000031000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000032000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000033000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000034000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000035000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000036000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000037000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000038000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000039000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000040000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000041000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000042000000}">
       <text>
         <r>
           <rPr>
@@ -2119,7 +2625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002F000000}">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000043000000}">
       <text>
         <r>
           <rPr>
@@ -2132,7 +2638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000030000000}">
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000044000000}">
       <text>
         <r>
           <rPr>
@@ -2146,7 +2652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000031000000}">
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000045000000}">
       <text>
         <r>
           <rPr>
@@ -2160,7 +2666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000032000000}">
+    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000046000000}">
       <text>
         <r>
           <rPr>
@@ -2174,7 +2680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000033000000}">
+    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000047000000}">
       <text>
         <r>
           <rPr>
@@ -2188,7 +2694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000034000000}">
+    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000048000000}">
       <text>
         <r>
           <rPr>
@@ -2201,7 +2707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000035000000}">
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000049000000}">
       <text>
         <r>
           <rPr>
@@ -2214,7 +2720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000036000000}">
+    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -2227,7 +2733,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000037000000}">
+    <comment ref="O31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -2240,7 +2746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000038000000}">
+    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -2253,7 +2759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000039000000}">
+    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -2266,7 +2772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003A000000}">
+    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004E000000}">
       <text>
         <r>
           <rPr>
@@ -2279,7 +2785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003B000000}">
+    <comment ref="O32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004F000000}">
       <text>
         <r>
           <rPr>
@@ -2292,7 +2798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003C000000}">
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000050000000}">
       <text>
         <r>
           <rPr>
@@ -2305,7 +2811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003D000000}">
+    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000051000000}">
       <text>
         <r>
           <rPr>
@@ -2318,7 +2824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003E000000}">
+    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2331,7 +2837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003F000000}">
+    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
       <text>
         <r>
           <rPr>
@@ -2344,7 +2850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000040000000}">
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
       <text>
         <r>
           <rPr>
@@ -2358,7 +2864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000041000000}">
+    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2372,7 +2878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000042000000}">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2386,7 +2892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000043000000}">
+    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2400,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000044000000}">
+    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2414,7 +2920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000045000000}">
+    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2428,7 +2934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000046000000}">
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2442,7 +2948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000047000000}">
+    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2456,7 +2962,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000048000000}">
+    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2470,7 +2976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000049000000}">
+    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2484,7 +2990,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004A000000}">
+    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2498,7 +3004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004B000000}">
+    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2512,7 +3018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004C000000}">
+    <comment ref="O35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2526,7 +3032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004D000000}">
+    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2539,7 +3045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004E000000}">
+    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -2552,7 +3058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004F000000}">
+    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -2565,7 +3071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000050000000}">
+    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -2578,7 +3084,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000051000000}">
+    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -2591,7 +3097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -2604,7 +3110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -2617,7 +3123,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -2630,7 +3162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -2644,7 +3176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -2658,7 +3190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -2672,7 +3204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -2686,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -2700,7 +3232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
       <text>
         <r>
           <rPr>
@@ -2714,7 +3246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -2728,7 +3260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -2742,7 +3274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -2756,7 +3288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -2770,7 +3302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -2784,7 +3316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -2798,7 +3330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -2812,7 +3344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -2826,7 +3358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -2840,7 +3372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -2854,7 +3386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -2867,7 +3399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -2880,7 +3412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -2893,7 +3425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -2906,7 +3438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -2919,7 +3451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -2932,7 +3464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -2945,7 +3477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -2958,7 +3490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
       <text>
         <r>
           <rPr>
@@ -2971,7 +3503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
       <text>
         <r>
           <rPr>
@@ -2984,7 +3516,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000085000000}">
       <text>
         <r>
           <rPr>
@@ -2997,7 +3529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000086000000}">
       <text>
         <r>
           <rPr>
@@ -3010,7 +3542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000087000000}">
       <text>
         <r>
           <rPr>
@@ -3024,7 +3556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000088000000}">
       <text>
         <r>
           <rPr>
@@ -3038,7 +3570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000089000000}">
       <text>
         <r>
           <rPr>
@@ -3052,7 +3584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008A000000}">
       <text>
         <r>
           <rPr>
@@ -3066,7 +3598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008B000000}">
       <text>
         <r>
           <rPr>
@@ -3080,7 +3612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008C000000}">
       <text>
         <r>
           <rPr>
@@ -3094,7 +3626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008D000000}">
       <text>
         <r>
           <rPr>
@@ -3108,7 +3640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008E000000}">
       <text>
         <r>
           <rPr>
@@ -3122,7 +3654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008F000000}">
       <text>
         <r>
           <rPr>
@@ -3136,7 +3668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000090000000}">
       <text>
         <r>
           <rPr>
@@ -3150,7 +3682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000091000000}">
       <text>
         <r>
           <rPr>
@@ -3164,7 +3696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000092000000}">
       <text>
         <r>
           <rPr>
@@ -3178,7 +3710,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000093000000}">
       <text>
         <r>
           <rPr>
@@ -3192,7 +3724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000094000000}">
       <text>
         <r>
           <rPr>
@@ -3205,7 +3737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000095000000}">
       <text>
         <r>
           <rPr>
@@ -3218,7 +3750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000096000000}">
       <text>
         <r>
           <rPr>
@@ -3231,7 +3763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000097000000}">
       <text>
         <r>
           <rPr>
@@ -3244,7 +3776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000098000000}">
       <text>
         <r>
           <rPr>
@@ -3257,7 +3789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+    <comment ref="E64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000099000000}">
       <text>
         <r>
           <rPr>
@@ -3270,7 +3802,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009C000000}">
       <text>
         <r>
           <rPr>
@@ -3874,88 +4432,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RRR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RRR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RRR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RRR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000019000000}">
+    <comment ref="F18" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000015000000}">
       <text>
         <r>
           <rPr>
@@ -3969,7 +4474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001A000000}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000016000000}">
       <text>
         <r>
           <rPr>
@@ -3983,7 +4488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001B000000}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000017000000}">
       <text>
         <r>
           <rPr>
@@ -3997,7 +4502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001C000000}">
+    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000018000000}">
       <text>
         <r>
           <rPr>
@@ -4010,7 +4515,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001D000000}">
+    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000019000000}">
       <text>
         <r>
           <rPr>
@@ -4023,7 +4528,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001E000000}">
+    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -4036,7 +4541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001F000000}">
+    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -4049,7 +4554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000020000000}">
+    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -4062,7 +4567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000021000000}">
+    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -4075,7 +4580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000022000000}">
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -4088,7 +4593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000023000000}">
+    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -4101,7 +4606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000024000000}">
+    <comment ref="G44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000020000000}">
       <text>
         <r>
           <rPr>
@@ -4114,7 +4619,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000025000000}">
+    <comment ref="H44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000021000000}">
       <text>
         <r>
           <rPr>
@@ -4127,7 +4632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000026000000}">
+    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000022000000}">
       <text>
         <r>
           <rPr>
@@ -4141,7 +4646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000027000000}">
+    <comment ref="E47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000023000000}">
       <text>
         <r>
           <rPr>
@@ -4155,7 +4660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000028000000}">
+    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000024000000}">
       <text>
         <r>
           <rPr>
@@ -4169,7 +4674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000029000000}">
+    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000025000000}">
       <text>
         <r>
           <rPr>
@@ -4183,7 +4688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002A000000}">
+    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000026000000}">
       <text>
         <r>
           <rPr>
@@ -4197,7 +4702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002B000000}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000027000000}">
       <text>
         <r>
           <rPr>
@@ -4212,7 +4717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002C000000}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000028000000}">
       <text>
         <r>
           <rPr>
@@ -4227,7 +4732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002D000000}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000029000000}">
       <text>
         <r>
           <rPr>
@@ -4242,7 +4747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002E000000}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -4257,7 +4762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002F000000}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -4272,7 +4777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000030000000}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -4286,7 +4791,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000031000000}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -4300,7 +4805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000032000000}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -4314,7 +4819,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000033000000}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002F000000}">
       <text>
         <r>
           <rPr>
@@ -4328,7 +4833,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000034000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000030000000}">
       <text>
         <r>
           <rPr>
@@ -4342,7 +4847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000035000000}">
+    <comment ref="D53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000031000000}">
       <text>
         <r>
           <rPr>
@@ -4355,7 +4860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000036000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000032000000}">
       <text>
         <r>
           <rPr>
@@ -4368,7 +4873,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000037000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000033000000}">
       <text>
         <r>
           <rPr>
@@ -4381,7 +4886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000038000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000034000000}">
       <text>
         <r>
           <rPr>
@@ -4394,7 +4899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000039000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000035000000}">
       <text>
         <r>
           <rPr>
@@ -4407,7 +4912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003A000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000036000000}">
       <text>
         <r>
           <rPr>
@@ -4420,7 +4925,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003B000000}">
+    <comment ref="H59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000037000000}">
       <text>
         <r>
           <rPr>
@@ -4433,7 +4938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003C000000}">
+    <comment ref="F61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000038000000}">
       <text>
         <r>
           <rPr>
@@ -4446,7 +4951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003D000000}">
+    <comment ref="G61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000039000000}">
       <text>
         <r>
           <rPr>
@@ -4459,7 +4964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003E000000}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003A000000}">
       <text>
         <r>
           <rPr>
@@ -4472,7 +4977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003F000000}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003B000000}">
       <text>
         <r>
           <rPr>
@@ -4485,7 +4990,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000040000000}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003C000000}">
       <text>
         <r>
           <rPr>
@@ -4498,7 +5003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000041000000}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003D000000}">
       <text>
         <r>
           <rPr>
@@ -4511,7 +5016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000042000000}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003E000000}">
       <text>
         <r>
           <rPr>
@@ -4524,7 +5029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000043000000}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003F000000}">
       <text>
         <r>
           <rPr>
@@ -4537,7 +5042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000044000000}">
+    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000040000000}">
       <text>
         <r>
           <rPr>
@@ -4550,7 +5055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000045000000}">
+    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000041000000}">
       <text>
         <r>
           <rPr>
@@ -4563,7 +5068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000046000000}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000042000000}">
       <text>
         <r>
           <rPr>
@@ -4576,7 +5081,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000047000000}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000043000000}">
       <text>
         <r>
           <rPr>
@@ -4589,88 +5094,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000048000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000049000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H73" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004E000000}">
+    <comment ref="F73" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000044000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F75" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000045000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000046000000}">
       <text>
         <r>
           <rPr>
@@ -4684,7 +5136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004F000000}">
+    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000047000000}">
       <text>
         <r>
           <rPr>
@@ -4698,7 +5150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000050000000}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000048000000}">
       <text>
         <r>
           <rPr>
@@ -4712,7 +5164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000051000000}">
+    <comment ref="D99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000049000000}">
       <text>
         <r>
           <rPr>
@@ -4725,7 +5177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000052000000}">
+    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -4738,7 +5190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000053000000}">
+    <comment ref="F99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -4751,7 +5203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000054000000}">
+    <comment ref="G99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -4764,7 +5216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000055000000}">
+    <comment ref="H99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -4777,7 +5229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000056000000}">
+    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004E000000}">
       <text>
         <r>
           <rPr>
@@ -4791,7 +5243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000057000000}">
+    <comment ref="E102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004F000000}">
       <text>
         <r>
           <rPr>
@@ -4805,7 +5257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000058000000}">
+    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000050000000}">
       <text>
         <r>
           <rPr>
@@ -4819,7 +5271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000059000000}">
+    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000051000000}">
       <text>
         <r>
           <rPr>
@@ -4833,7 +5285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005A000000}">
+    <comment ref="H102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000052000000}">
       <text>
         <r>
           <rPr>
@@ -4847,7 +5299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005B000000}">
+    <comment ref="D104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000053000000}">
       <text>
         <r>
           <rPr>
@@ -4862,7 +5314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005C000000}">
+    <comment ref="E104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000054000000}">
       <text>
         <r>
           <rPr>
@@ -4877,7 +5329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005D000000}">
+    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000055000000}">
       <text>
         <r>
           <rPr>
@@ -4892,7 +5344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005E000000}">
+    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000056000000}">
       <text>
         <r>
           <rPr>
@@ -4907,7 +5359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005F000000}">
+    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000057000000}">
       <text>
         <r>
           <rPr>
@@ -4922,7 +5374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000060000000}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000058000000}">
       <text>
         <r>
           <rPr>
@@ -4936,7 +5388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000061000000}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000059000000}">
       <text>
         <r>
           <rPr>
@@ -4950,7 +5402,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000062000000}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -4964,7 +5416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000063000000}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -4978,7 +5430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000064000000}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -4992,7 +5444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000065000000}">
+    <comment ref="D108" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -5005,7 +5457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000066000000}">
+    <comment ref="F113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -5018,7 +5470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000067000000}">
+    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -5031,7 +5483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000068000000}">
+    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000060000000}">
       <text>
         <r>
           <rPr>
@@ -5044,7 +5496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000069000000}">
+    <comment ref="F114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000061000000}">
       <text>
         <r>
           <rPr>
@@ -5057,7 +5509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006A000000}">
+    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000062000000}">
       <text>
         <r>
           <rPr>
@@ -5070,7 +5522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006B000000}">
+    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000063000000}">
       <text>
         <r>
           <rPr>
@@ -5083,7 +5535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006C000000}">
+    <comment ref="F116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000064000000}">
       <text>
         <r>
           <rPr>
@@ -5096,7 +5548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006D000000}">
+    <comment ref="G116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000065000000}">
       <text>
         <r>
           <rPr>
@@ -5109,7 +5561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006E000000}">
+    <comment ref="F118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000066000000}">
       <text>
         <r>
           <rPr>
@@ -5122,7 +5574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006F000000}">
+    <comment ref="G118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000067000000}">
       <text>
         <r>
           <rPr>
@@ -5135,7 +5587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000070000000}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000068000000}">
       <text>
         <r>
           <rPr>
@@ -5148,7 +5600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000071000000}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000069000000}">
       <text>
         <r>
           <rPr>
@@ -5161,7 +5613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000072000000}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -5174,7 +5626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000073000000}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -5187,7 +5639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000074000000}">
+    <comment ref="F124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -5200,7 +5652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000075000000}">
+    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -5213,7 +5665,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000076000000}">
+    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -5226,7 +5678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000077000000}">
+    <comment ref="G126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -5239,88 +5691,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000078000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000079000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H128" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H130" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007E000000}">
+    <comment ref="F128" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000070000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000071000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000072000000}">
       <text>
         <r>
           <rPr>
@@ -5334,7 +5733,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007F000000}">
+    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000073000000}">
       <text>
         <r>
           <rPr>
@@ -5348,7 +5747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000080000000}">
+    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000074000000}">
       <text>
         <r>
           <rPr>
@@ -5362,7 +5761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000081000000}">
+    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000075000000}">
       <text>
         <r>
           <rPr>
@@ -5375,7 +5774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000082000000}">
+    <comment ref="E154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000076000000}">
       <text>
         <r>
           <rPr>
@@ -5388,7 +5787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000083000000}">
+    <comment ref="F154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000077000000}">
       <text>
         <r>
           <rPr>
@@ -5401,7 +5800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000084000000}">
+    <comment ref="G154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000078000000}">
       <text>
         <r>
           <rPr>
@@ -5414,7 +5813,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000085000000}">
+    <comment ref="H154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000079000000}">
       <text>
         <r>
           <rPr>
@@ -5427,7 +5826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000086000000}">
+    <comment ref="D157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -5441,7 +5840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000087000000}">
+    <comment ref="E157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -5455,7 +5854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000088000000}">
+    <comment ref="F157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -5469,7 +5868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000089000000}">
+    <comment ref="G157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -5483,7 +5882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008A000000}">
+    <comment ref="H157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -5497,7 +5896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008B000000}">
+    <comment ref="D159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -5512,7 +5911,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008C000000}">
+    <comment ref="E159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000080000000}">
       <text>
         <r>
           <rPr>
@@ -5527,7 +5926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008D000000}">
+    <comment ref="F159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000081000000}">
       <text>
         <r>
           <rPr>
@@ -5542,7 +5941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008E000000}">
+    <comment ref="G159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000082000000}">
       <text>
         <r>
           <rPr>
@@ -5557,7 +5956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008F000000}">
+    <comment ref="H159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000083000000}">
       <text>
         <r>
           <rPr>
@@ -5572,7 +5971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000090000000}">
+    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000084000000}">
       <text>
         <r>
           <rPr>
@@ -5586,7 +5985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000091000000}">
+    <comment ref="E161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000085000000}">
       <text>
         <r>
           <rPr>
@@ -5600,7 +5999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000092000000}">
+    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000086000000}">
       <text>
         <r>
           <rPr>
@@ -5614,7 +6013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000093000000}">
+    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000087000000}">
       <text>
         <r>
           <rPr>
@@ -5628,7 +6027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000094000000}">
+    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000088000000}">
       <text>
         <r>
           <rPr>
@@ -5642,7 +6041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000095000000}">
+    <comment ref="D163" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000089000000}">
       <text>
         <r>
           <rPr>
@@ -5674,7 +6073,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
 RRR=1-1*0.17=0.83</t>
         </r>
       </text>
@@ -5688,7 +6087,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
 RRR=1-1*0.17=0.83</t>
         </r>
       </text>
@@ -5702,7 +6101,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
 RRR=1-1*0.17=0.83</t>
         </r>
       </text>
@@ -5716,7 +6115,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
 RRR=1-1*0.17=0.83</t>
         </r>
       </text>
@@ -7336,7 +7735,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="341">
   <si>
     <t>Baseline year data</t>
   </si>
@@ -9788,7 +10187,7 @@
         <v>168</v>
       </c>
       <c r="B3" s="45">
-        <v>0.2066742856206</v>
+        <v>0</v>
       </c>
       <c r="C3" s="98">
         <v>0.95</v>
@@ -10087,7 +10486,7 @@
         <v>181</v>
       </c>
       <c r="B16" s="45">
-        <v>0.95</v>
+        <v>7.8606899999999993E-2</v>
       </c>
       <c r="C16" s="98">
         <v>0.95</v>
@@ -10133,7 +10532,7 @@
         <v>148</v>
       </c>
       <c r="B18" s="98">
-        <v>0.11733278925379</v>
+        <v>7.7588900000000002E-2</v>
       </c>
       <c r="C18" s="98">
         <v>0.95</v>
@@ -10156,7 +10555,7 @@
         <v>151</v>
       </c>
       <c r="B19" s="98">
-        <v>0.89972340000000006</v>
+        <v>7.7588900000000002E-2</v>
       </c>
       <c r="C19" s="98">
         <v>0.95</v>
@@ -10202,7 +10601,7 @@
         <v>183</v>
       </c>
       <c r="B21" s="45">
-        <v>0.80314839999999998</v>
+        <v>0</v>
       </c>
       <c r="C21" s="98">
         <v>0.95</v>
@@ -10248,7 +10647,7 @@
         <v>185</v>
       </c>
       <c r="B23" s="98">
-        <v>0</v>
+        <v>3.9129999999999998E-3</v>
       </c>
       <c r="C23" s="98">
         <v>0.95</v>
@@ -10271,7 +10670,7 @@
         <v>186</v>
       </c>
       <c r="B24" s="45">
-        <v>0.88910919143547995</v>
+        <v>0.66624536519805999</v>
       </c>
       <c r="C24" s="98">
         <v>0.95</v>
@@ -10363,7 +10762,7 @@
         <v>190</v>
       </c>
       <c r="B28" s="45">
-        <v>0.69723745018169003</v>
+        <v>0.45581739999999998</v>
       </c>
       <c r="C28" s="98">
         <v>0.95</v>
@@ -10386,7 +10785,7 @@
         <v>191</v>
       </c>
       <c r="B29" s="45">
-        <v>0</v>
+        <v>0.23215369999999999</v>
       </c>
       <c r="C29" s="98">
         <v>0.95</v>
@@ -10478,7 +10877,7 @@
         <v>194</v>
       </c>
       <c r="B33" s="45">
-        <v>0</v>
+        <v>0.72116230000000003</v>
       </c>
       <c r="C33" s="98">
         <v>0.95</v>
@@ -10501,7 +10900,7 @@
         <v>195</v>
       </c>
       <c r="B34" s="45">
-        <v>0</v>
+        <v>0.12046129999999999</v>
       </c>
       <c r="C34" s="98">
         <v>0.95</v>
@@ -10547,7 +10946,7 @@
         <v>197</v>
       </c>
       <c r="B36" s="45">
-        <v>0.23215369999999999</v>
+        <v>5.8989100000000003E-2</v>
       </c>
       <c r="C36" s="98">
         <v>0.95</v>
@@ -10570,7 +10969,7 @@
         <v>198</v>
       </c>
       <c r="B37" s="45">
-        <v>0</v>
+        <v>0.80314839999999998</v>
       </c>
       <c r="C37" s="98">
         <v>0.95</v>
@@ -10593,7 +10992,7 @@
         <v>199</v>
       </c>
       <c r="B38" s="45">
-        <v>0.45581739999999998</v>
+        <v>0</v>
       </c>
       <c r="C38" s="98">
         <v>0.95</v>
@@ -10635,7 +11034,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SwqShMKjZ/Tc3FrdHQz/MjdsWftRTk85s02s32k0tDk98bBhXaGhkqbuII/OivPUJtqXOhQ4ck/oX/RBAeMIgQ==" saltValue="RORLzDUZEp7fquGh4DZ5hw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7vflRb+A4U2pEdxn7m/v0lFZNI78qfZXbnYBjV1V9XLM+tHWxQCvL8xYVSz8kIygwB6Bp0chVfPhUDXzL0eOkw==" saltValue="BwzbjGZ5GxwK0BvfdhnvSQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10668,7 +11067,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>179</v>
       </c>
@@ -10677,7 +11076,7 @@
       </c>
       <c r="C2" s="47"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
         <v>180</v>
       </c>
@@ -10686,7 +11085,7 @@
       </c>
       <c r="C3" s="47"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>191</v>
       </c>
@@ -10695,7 +11094,7 @@
       </c>
       <c r="C4" s="47"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="57" t="s">
         <v>188</v>
       </c>
@@ -10704,7 +11103,7 @@
       </c>
       <c r="C5" s="47"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57" t="s">
         <v>191</v>
       </c>
@@ -10713,7 +11112,7 @@
       </c>
       <c r="C6" s="58"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57" t="s">
         <v>188</v>
       </c>
@@ -10722,7 +11121,7 @@
       </c>
       <c r="C7" s="58"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="57" t="s">
         <v>200</v>
       </c>
@@ -10731,7 +11130,7 @@
       </c>
       <c r="C8" s="58"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
         <v>193</v>
       </c>
@@ -10740,37 +11139,37 @@
       </c>
       <c r="C9" s="58"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="59"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="59"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="59"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
@@ -10821,65 +11220,67 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -14859,7 +15260,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>166</v>
       </c>
@@ -14876,7 +15277,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>168</v>
       </c>
@@ -14893,7 +15294,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>169</v>
       </c>
@@ -14910,7 +15311,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>170</v>
       </c>
@@ -14927,7 +15328,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>171</v>
       </c>
@@ -14946,7 +15347,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>172</v>
       </c>
@@ -14965,7 +15366,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>173</v>
       </c>
@@ -14984,7 +15385,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>174</v>
       </c>
@@ -15003,7 +15404,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>175</v>
       </c>
@@ -15020,7 +15421,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>176</v>
       </c>
@@ -15037,7 +15438,7 @@
       <c r="J11" s="87"/>
       <c r="K11" s="87"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>177</v>
       </c>
@@ -15054,7 +15455,7 @@
       <c r="J12" s="87"/>
       <c r="K12" s="87"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>178</v>
       </c>
@@ -15071,7 +15472,7 @@
       <c r="J13" s="87"/>
       <c r="K13" s="87"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>179</v>
       </c>
@@ -15090,7 +15491,7 @@
       <c r="J14" s="87"/>
       <c r="K14" s="87"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>180</v>
       </c>
@@ -15109,7 +15510,7 @@
       <c r="J15" s="87"/>
       <c r="K15" s="87"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>181</v>
       </c>
@@ -15622,7 +16023,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>67</v>
       </c>
@@ -15651,7 +16052,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>77</v>
       </c>
@@ -15680,7 +16081,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>78</v>
       </c>
@@ -15709,7 +16110,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>79</v>
       </c>
@@ -15738,7 +16139,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>80</v>
       </c>
@@ -15767,7 +16168,7 @@
       <c r="J6" s="87"/>
       <c r="K6" s="87"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>112</v>
       </c>
@@ -15788,7 +16189,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>113</v>
       </c>
@@ -15809,7 +16210,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>114</v>
       </c>
@@ -15830,7 +16231,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>115</v>
       </c>
@@ -15851,7 +16252,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>58</v>
       </c>
@@ -15872,7 +16273,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>59</v>
       </c>
@@ -15891,7 +16292,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>60</v>
       </c>
@@ -15910,7 +16311,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>61</v>
       </c>
@@ -16858,7 +17259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="104"/>
       <c r="C3" s="8" t="s">
         <v>146</v>
@@ -16880,7 +17281,7 @@
       </c>
       <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="104"/>
       <c r="C4" s="8" t="s">
         <v>147</v>
@@ -16902,7 +17303,7 @@
       </c>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="103" t="s">
         <v>67</v>
       </c>
@@ -16925,7 +17326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="104"/>
       <c r="C6" s="8" t="s">
         <v>146</v>
@@ -16946,7 +17347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="104"/>
       <c r="C7" s="8" t="s">
         <v>147</v>
@@ -16967,7 +17368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="103" t="s">
         <v>77</v>
       </c>
@@ -16990,7 +17391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="104"/>
       <c r="C9" s="8" t="s">
         <v>146</v>
@@ -17011,7 +17412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="104"/>
       <c r="C10" s="8" t="s">
         <v>147</v>
@@ -17032,7 +17433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="103" t="s">
         <v>78</v>
       </c>
@@ -17055,7 +17456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="104"/>
       <c r="C12" s="8" t="s">
         <v>146</v>
@@ -17076,7 +17477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="104"/>
       <c r="C13" s="8" t="s">
         <v>147</v>
@@ -17097,7 +17498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="103" t="s">
         <v>79</v>
       </c>
@@ -17120,7 +17521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="104"/>
       <c r="C15" s="8" t="s">
         <v>146</v>
@@ -17141,7 +17542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="104"/>
       <c r="C16" s="8" t="s">
         <v>147</v>
@@ -17185,7 +17586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="86"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
@@ -20578,12 +20979,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -20593,36 +21018,12 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23554,7 +23955,7 @@
         <v>119</v>
       </c>
       <c r="D66" s="90">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="E66" s="89">
         <v>1</v>
@@ -23669,7 +24070,7 @@
         <v>119</v>
       </c>
       <c r="D70" s="90">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="E70" s="89">
         <v>1</v>
@@ -23784,7 +24185,7 @@
         <v>119</v>
       </c>
       <c r="D74" s="90">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="E74" s="89">
         <v>1</v>
@@ -26287,7 +26688,7 @@
       </c>
       <c r="D176" s="91">
         <f t="shared" ref="D176:G195" si="7">IF(D66=1,1,D66*0.9)</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E176" s="91">
         <f t="shared" si="7"/>
@@ -26386,7 +26787,7 @@
       </c>
       <c r="D180" s="91">
         <f t="shared" si="7"/>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E180" s="91">
         <f t="shared" si="7"/>
@@ -26485,7 +26886,7 @@
       </c>
       <c r="D184" s="91">
         <f t="shared" si="7"/>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E184" s="91">
         <f t="shared" si="7"/>
@@ -28913,7 +29314,7 @@
       </c>
       <c r="D286" s="91">
         <f t="shared" ref="D286:G305" si="17">IF(D66=1,1,D66*1.1)</f>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E286" s="91">
         <f t="shared" si="17"/>
@@ -29016,7 +29417,7 @@
       </c>
       <c r="D290" s="91">
         <f t="shared" si="17"/>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E290" s="91">
         <f t="shared" si="17"/>
@@ -29119,7 +29520,7 @@
       </c>
       <c r="D294" s="91">
         <f t="shared" si="17"/>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E294" s="91">
         <f t="shared" si="17"/>
@@ -29973,7 +30374,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1gEiboypgN1VYdmLYuHEsviiXDH91vsC32xKqzOEbclcsh2pOXs0vX071vry3NRJsC+T2/BNfpXbXWW7dldjVQ==" saltValue="XZihSWmo245BlR0GYalydw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QPUFmCFtFBVVyEMWX+ufO46C8X+nKRCwHNyDvv7CKg/oO7DPZp1nYnOMxNvnqXsQKuBxQKlHWKOifwOzFAazNA==" saltValue="HCEWU6EJTzcX+etfLOPz7w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -30202,19 +30603,19 @@
         <v>288</v>
       </c>
       <c r="C15" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D15" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E15" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F15" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G15" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -30223,19 +30624,19 @@
         <v>289</v>
       </c>
       <c r="C16" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D16" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E16" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F16" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G16" s="90">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -30365,24 +30766,19 @@
         <v>293</v>
       </c>
       <c r="C27" s="90">
-        <f>IF(C4=1,1,C4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="D27" s="90">
-        <f>IF(D4=1,1,D4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="E27" s="90">
-        <f>IF(E4=1,1,E4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="F27" s="90">
-        <f>IF(F4=1,1,F4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="G27" s="90">
-        <f>IF(G4=1,1,G4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -30549,24 +30945,19 @@
         <v>301</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" ref="C38:G40" si="1">IF(C15=1,1,C15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E38" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F38" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -30575,24 +30966,19 @@
         <v>302</v>
       </c>
       <c r="C39" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D39" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E39" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F39" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G39" s="90">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -30603,23 +30989,23 @@
         <v>303</v>
       </c>
       <c r="C40" s="90">
-        <f t="shared" si="1"/>
+        <f>IF(C17=1,1,C17*0.9)</f>
         <v>1</v>
       </c>
       <c r="D40" s="90">
-        <f t="shared" si="1"/>
+        <f>IF(D17=1,1,D17*0.9)</f>
         <v>1</v>
       </c>
       <c r="E40" s="90">
-        <f t="shared" si="1"/>
+        <f>IF(E17=1,1,E17*0.9)</f>
         <v>1</v>
       </c>
       <c r="F40" s="90">
-        <f t="shared" si="1"/>
+        <f>IF(F17=1,1,F17*0.9)</f>
         <v>1</v>
       </c>
       <c r="G40" s="90">
-        <f t="shared" si="1"/>
+        <f>IF(G17=1,1,G17*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -30714,19 +31100,19 @@
         <v>283</v>
       </c>
       <c r="D49" s="90">
-        <f t="shared" ref="D49:G50" si="2">D3*1.05</f>
+        <f>D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" si="2"/>
+        <f>E3*1.05</f>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="2"/>
+        <f>F3*1.05</f>
         <v>183.435</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="2"/>
+        <f>G3*1.05</f>
         <v>183.435</v>
       </c>
     </row>
@@ -30736,24 +31122,19 @@
         <v>307</v>
       </c>
       <c r="C50" s="90">
-        <f>C4*1.05</f>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="2"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="2"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="2"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="2"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -30766,11 +31147,11 @@
         <v>309</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" ref="C52:D55" si="3">IF(C6=1,1,C6*1.1)</f>
+        <f t="shared" ref="C52:D55" si="1">IF(C6=1,1,C6*1.1)</f>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
@@ -30791,11 +31172,11 @@
         <v>310</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
@@ -30814,11 +31195,11 @@
         <v>311</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
@@ -30837,11 +31218,11 @@
         <v>312</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
@@ -30920,24 +31301,19 @@
         <v>315</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" ref="C61:G63" si="4">IF(C15=1,1,C15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E61" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F61" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -30946,24 +31322,19 @@
         <v>316</v>
       </c>
       <c r="C62" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D62" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E62" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F62" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G62" s="90">
-        <f t="shared" si="4"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -30974,23 +31345,23 @@
         <v>317</v>
       </c>
       <c r="C63" s="90">
-        <f t="shared" si="4"/>
+        <f>IF(C17=1,1,C17*1.1)</f>
         <v>1</v>
       </c>
       <c r="D63" s="90">
-        <f t="shared" si="4"/>
+        <f>IF(D17=1,1,D17*1.1)</f>
         <v>1</v>
       </c>
       <c r="E63" s="90">
-        <f t="shared" si="4"/>
+        <f>IF(E17=1,1,E17*1.1)</f>
         <v>1</v>
       </c>
       <c r="F63" s="90">
-        <f t="shared" si="4"/>
+        <f>IF(F17=1,1,F17*1.1)</f>
         <v>1</v>
       </c>
       <c r="G63" s="90">
-        <f t="shared" si="4"/>
+        <f>IF(G17=1,1,G17*1.1)</f>
         <v>1</v>
       </c>
     </row>
@@ -32525,37 +32896,37 @@
         <v>1</v>
       </c>
       <c r="E18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O18" s="90">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -32613,47 +32984,36 @@
         <v>1</v>
       </c>
       <c r="E20" s="90">
-        <f t="shared" ref="E20:O20" si="0">E19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="90">
-        <f t="shared" si="0"/>
         <v>0.97599999999999998</v>
       </c>
     </row>
@@ -32765,47 +33125,47 @@
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -32814,23 +33174,23 @@
         <v>175</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32846,19 +33206,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32867,23 +33227,23 @@
         <v>176</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32899,19 +33259,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32920,23 +33280,23 @@
         <v>177</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -32952,19 +33312,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32973,23 +33333,23 @@
         <v>178</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -33005,19 +33365,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -33026,39 +33386,39 @@
         <v>179</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33079,39 +33439,39 @@
         <v>180</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33132,39 +33492,39 @@
         <v>181</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33202,19 +33562,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33283,11 +33643,11 @@
         <v>188</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33300,35 +33660,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -33337,39 +33697,39 @@
         <v>189</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
@@ -33390,11 +33750,11 @@
         <v>192</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33404,39 +33764,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -33451,56 +33811,45 @@
         <v>172</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:D44" si="8">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -33508,11 +33857,11 @@
         <v>173</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
@@ -33554,56 +33903,45 @@
         <v>174</v>
       </c>
       <c r="C43" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D43" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="11"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -33611,11 +33949,11 @@
         <v>182</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
@@ -33716,47 +34054,47 @@
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="9">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -33765,23 +34103,23 @@
         <v>175</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="10">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33797,19 +34135,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="11">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33818,23 +34156,23 @@
         <v>176</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33850,19 +34188,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33871,23 +34209,23 @@
         <v>177</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -33903,19 +34241,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33924,23 +34262,23 @@
         <v>178</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -33956,19 +34294,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -33977,39 +34315,39 @@
         <v>179</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="12">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -34030,39 +34368,39 @@
         <v>180</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34083,39 +34421,39 @@
         <v>181</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
@@ -34154,19 +34492,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34235,11 +34573,11 @@
         <v>188</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="13">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34252,35 +34590,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="14">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34289,39 +34627,39 @@
         <v>189</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="15">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
@@ -34342,11 +34680,11 @@
         <v>192</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34356,39 +34694,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="16">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
@@ -34403,56 +34741,45 @@
         <v>172</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="17">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.25">
@@ -34460,11 +34787,11 @@
         <v>173</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
@@ -34506,56 +34833,45 @@
         <v>174</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="22"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -34563,11 +34879,11 @@
         <v>182</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
@@ -34651,7 +34967,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>157</v>
       </c>
@@ -34686,7 +35002,7 @@
       <c r="F4" s="83"/>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>158</v>
       </c>
@@ -34739,7 +35055,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>157</v>
       </c>
@@ -34774,7 +35090,7 @@
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>158</v>
       </c>
@@ -34827,7 +35143,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>157</v>
       </c>
@@ -34862,7 +35178,7 @@
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>158</v>
       </c>
@@ -34940,7 +35256,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>193</v>
       </c>
@@ -34966,7 +35282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
         <v>339</v>
       </c>
@@ -34986,7 +35302,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
         <v>340</v>
       </c>
@@ -35006,7 +35322,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>191</v>
       </c>
@@ -35032,7 +35348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>340</v>
       </c>
@@ -35052,7 +35368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
@@ -35075,7 +35391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>340</v>
       </c>
@@ -35095,7 +35411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>184</v>
       </c>
@@ -35121,7 +35437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>340</v>
       </c>
@@ -35141,7 +35457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>204</v>
       </c>
@@ -35164,7 +35480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>340</v>
       </c>
@@ -35184,7 +35500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>192</v>
       </c>
@@ -35210,7 +35526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>340</v>
       </c>
@@ -35230,7 +35546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>204</v>
       </c>
@@ -35253,7 +35569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>340</v>
       </c>
@@ -35273,7 +35589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>169</v>
       </c>
@@ -35299,7 +35615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="5" t="s">
         <v>340</v>
       </c>
@@ -35310,16 +35626,19 @@
         <v>0</v>
       </c>
       <c r="F18" s="90">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_6_11months+(frac_sam_6_11months*0.89)),0),1)</f>
+        <v>0.10931371107271459</v>
       </c>
       <c r="G18" s="90">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_12_23months+(frac_sam_12_23months*0.89)),0),1)</f>
+        <v>0.10819103507575045</v>
       </c>
       <c r="H18" s="90">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>MIN(MAX(1-0.89/(1-frac_sam_24_59months+(frac_sam_24_59months*0.89)),0),1)</f>
+        <v>0.10934904726622252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>204</v>
       </c>
@@ -35342,7 +35661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
         <v>340</v>
       </c>
@@ -35353,13 +35672,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="90">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_6_11months+(frac_mam_6_11months*0.89)),0),1)</f>
+        <v>0.10235156587109062</v>
       </c>
       <c r="G20" s="90">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_12_23months+(frac_mam_12_23months*0.89)),0),1)</f>
+        <v>0.1052274811290691</v>
       </c>
       <c r="H20" s="90">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_24_59months+(frac_mam_24_59months*0.89)),0),1)</f>
+        <v>0.10624060847171513</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -36527,13 +36849,16 @@
         <v>0</v>
       </c>
       <c r="F73" s="90">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_6_11months+(frac_sam_6_11months*0.99)),0),1)</f>
+        <v>9.9306486121433224E-3</v>
       </c>
       <c r="G73" s="90">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_12_23months+(frac_sam_12_23months*0.99)),0),1)</f>
+        <v>9.8174083497344355E-3</v>
       </c>
       <c r="H73" s="90">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_24_59months+(frac_sam_24_59months*0.99)),0),1)</f>
+        <v>9.9342170591840695E-3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -36552,15 +36877,12 @@
         <v>0</v>
       </c>
       <c r="F74" s="90">
-        <f>IF($C19="Affected fraction",F19,IF(F19=1,1,F19*0.9))</f>
         <v>1</v>
       </c>
       <c r="G74" s="90">
-        <f>IF($C19="Affected fraction",G19,IF(G19=1,1,G19*0.9))</f>
         <v>1</v>
       </c>
       <c r="H74" s="90">
-        <f>IF($C19="Affected fraction",H19,IF(H19=1,1,H19*0.9))</f>
         <v>1</v>
       </c>
     </row>
@@ -36577,13 +36899,16 @@
         <v>0</v>
       </c>
       <c r="F75" s="90">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_6_11months+(frac_mam_6_11months*0.99)),0),1)</f>
+        <v>9.2325584751669076E-3</v>
       </c>
       <c r="G75" s="90">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_12_23months+(frac_mam_12_23months*0.99)),0),1)</f>
+        <v>9.5197270109106391E-3</v>
       </c>
       <c r="H75" s="90">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_24_59months+(frac_mam_24_59months*0.99)),0),1)</f>
+        <v>9.6212910662482054E-3</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -37783,13 +38108,16 @@
         <v>0</v>
       </c>
       <c r="F128" s="90">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_6_11months+(frac_sam_6_11months*0.8)),0),1)</f>
+        <v>0.19887767569098247</v>
       </c>
       <c r="G128" s="90">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_12_23months+(frac_sam_12_23months*0.8)),0),1)</f>
+        <v>0.19703864640950408</v>
       </c>
       <c r="H128" s="90">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_24_59months+(frac_sam_24_59months*0.8)),0),1)</f>
+        <v>0.19893549742510819</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -37808,15 +38136,12 @@
         <v>0</v>
       </c>
       <c r="F129" s="90">
-        <f>IF($C74="Affected fraction",F74,IF(F74=1,1,F74*0.9))</f>
         <v>1</v>
       </c>
       <c r="G129" s="90">
-        <f>IF($C74="Affected fraction",G74,IF(G74=1,1,G74*0.9))</f>
         <v>1</v>
       </c>
       <c r="H129" s="90">
-        <f>IF($C74="Affected fraction",H74,IF(H74=1,1,H74*0.9))</f>
         <v>1</v>
       </c>
     </row>
@@ -37833,13 +38158,16 @@
         <v>0</v>
       </c>
       <c r="F130" s="90">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_6_11months+(frac_mam_6_11months*0.8)),0),1)</f>
+        <v>0.18741149260584067</v>
       </c>
       <c r="G130" s="90">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_12_23months+(frac_mam_12_23months*0.8)),0),1)</f>
+        <v>0.19216580166810082</v>
       </c>
       <c r="H130" s="90">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_24_59months+(frac_mam_24_59months*0.8)),0),1)</f>
+        <v>0.19383464081262103</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -38660,7 +38988,7 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -38684,25 +39012,25 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
         <v>339</v>
       </c>
       <c r="D3" s="90">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="E3" s="90">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="F3" s="90">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="G3" s="90">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>187</v>
       </c>
@@ -38726,7 +39054,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="8" t="s">
         <v>339</v>
       </c>
@@ -38744,7 +39072,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>186</v>
       </c>
@@ -38768,7 +39096,7 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="8" t="s">
         <v>339</v>
       </c>
@@ -38812,7 +39140,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>168</v>
       </c>
@@ -38839,7 +39167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
         <v>339</v>
       </c>
@@ -38856,7 +39184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>187</v>
       </c>
@@ -38883,7 +39211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
         <v>339</v>
       </c>
@@ -38904,7 +39232,7 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>186</v>
       </c>
@@ -38931,7 +39259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
         <v>339</v>
       </c>
@@ -39010,16 +39338,16 @@
         <v>339</v>
       </c>
       <c r="D21" s="90">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="E21" s="90">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="F21" s="90">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G21" s="90">
-        <v>0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -40154,7 +40482,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -40171,10 +40499,10 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -40191,10 +40519,10 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -40211,7 +40539,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>90</v>
       </c>
@@ -40225,7 +40553,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>129</v>
       </c>
@@ -40239,7 +40567,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>130</v>
       </c>
@@ -40256,7 +40584,7 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>132</v>
       </c>
@@ -40270,7 +40598,7 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>32</v>
       </c>
@@ -40287,7 +40615,7 @@
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>134</v>
       </c>
@@ -40327,7 +40655,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>137</v>
       </c>
@@ -40335,7 +40663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>138</v>
       </c>
@@ -40343,7 +40671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>139</v>
       </c>
@@ -40351,7 +40679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>140</v>
       </c>
@@ -40359,7 +40687,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>141</v>
       </c>
@@ -40367,7 +40695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>142</v>
       </c>
@@ -40428,7 +40756,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
         <v>67</v>
       </c>
@@ -40441,7 +40769,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>77</v>
       </c>
@@ -40454,7 +40782,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
         <v>78</v>
       </c>
@@ -40467,7 +40795,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>79</v>
       </c>
@@ -40480,7 +40808,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
         <v>150</v>
       </c>
@@ -40502,7 +40830,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>67</v>
       </c>
@@ -40513,7 +40841,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>77</v>
       </c>
@@ -40524,7 +40852,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="32" t="s">
         <v>78</v>
       </c>
@@ -40537,7 +40865,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="32" t="s">
         <v>79</v>
       </c>
@@ -40550,7 +40878,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
         <v>150</v>
       </c>

--- a/inputs/en/LiST countries/SYR_databook.xlsx
+++ b/inputs/en/LiST countries/SYR_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A4BE210-6C2D-491C-9C1C-AC4C08F612D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{329C67C1-2979-4CDF-9612-51F2764FF944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="961" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Baseline year population inputs'!$C$47</definedName>
     <definedName name="U5_mortality">'Baseline year population inputs'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -909,16 +909,16 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-OR = 1.50 (1.26-1.78) for exclusive breastfeeding in children &lt; 1 month.</t>
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Impact on &lt;1 month not considered to avoid double counting with the mortality benefits for this age group</t>
         </r>
       </text>
     </comment>
@@ -1060,7 +1060,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Impact on &lt;1 month not considered to avoid double counting with the mortality benefits for this age group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1073,7 +1086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1088,7 +1101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
+    <comment ref="C39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
       <text>
         <r>
           <rPr>
@@ -1103,7 +1116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -1116,7 +1129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -1130,7 +1143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -1143,7 +1156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -1156,7 +1169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001D000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -1170,7 +1183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001E000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -1184,7 +1197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001F000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000020000000}">
       <text>
         <r>
           <rPr>
@@ -1198,7 +1211,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="C61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000020000000}">
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000021000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Impact on &lt;1 month not considered to avoid double counting with the mortality benefits for this age group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000022000000}">
       <text>
         <r>
           <rPr>
@@ -1213,7 +1239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000021000000}">
+    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000023000000}">
       <text>
         <r>
           <rPr>
@@ -1750,11 +1776,39 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000002000000}">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1768,7 +1822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000003000000}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1781,7 +1835,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000004000000}">
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1794,7 +1848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000005000000}">
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1807,7 +1861,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000006000000}">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1820,7 +1874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000007000000}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1833,7 +1887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000008000000}">
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -1846,7 +1900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000009000000}">
+    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -1859,7 +1913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000A000000}">
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -1872,7 +1926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000B000000}">
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -1885,7 +1939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000C000000}">
+    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -1898,7 +1952,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000D000000}">
+    <comment ref="O9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -1911,7 +1965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000E000000}">
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000010000000}">
       <text>
         <r>
           <rPr>
@@ -1924,7 +1978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00000F000000}">
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000011000000}">
       <text>
         <r>
           <rPr>
@@ -1937,7 +1991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000010000000}">
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000012000000}">
       <text>
         <r>
           <rPr>
@@ -1950,7 +2004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000011000000}">
+    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000013000000}">
       <text>
         <r>
           <rPr>
@@ -1963,7 +2017,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000012000000}">
+    <comment ref="E11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000014000000}">
       <text>
         <r>
           <rPr>
@@ -1976,7 +2030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000013000000}">
+    <comment ref="F11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000015000000}">
       <text>
         <r>
           <rPr>
@@ -1989,7 +2043,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000014000000}">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000016000000}">
       <text>
         <r>
           <rPr>
@@ -2003,7 +2057,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000015000000}">
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000017000000}">
       <text>
         <r>
           <rPr>
@@ -2017,7 +2071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000016000000}">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000018000000}">
       <text>
         <r>
           <rPr>
@@ -2031,7 +2085,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000017000000}">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000019000000}">
       <text>
         <r>
           <rPr>
@@ -2045,7 +2099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000018000000}">
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -2059,7 +2113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000019000000}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -2073,7 +2127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001A000000}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -2087,7 +2141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001B000000}">
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -2101,7 +2155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001C000000}">
+    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -2115,7 +2169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001D000000}">
+    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -2129,7 +2183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001E000000}">
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000020000000}">
       <text>
         <r>
           <rPr>
@@ -2143,7 +2197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00001F000000}">
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000021000000}">
       <text>
         <r>
           <rPr>
@@ -2157,7 +2211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000020000000}">
+    <comment ref="O12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000022000000}">
       <text>
         <r>
           <rPr>
@@ -2171,7 +2225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000021000000}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000023000000}">
       <text>
         <r>
           <rPr>
@@ -2184,7 +2238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000022000000}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000024000000}">
       <text>
         <r>
           <rPr>
@@ -2197,7 +2251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000023000000}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000025000000}">
       <text>
         <r>
           <rPr>
@@ -2210,7 +2264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000024000000}">
+    <comment ref="L14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000026000000}">
       <text>
         <r>
           <rPr>
@@ -2226,7 +2280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000025000000}">
+    <comment ref="M14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000027000000}">
       <text>
         <r>
           <rPr>
@@ -2242,7 +2296,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000026000000}">
+    <comment ref="N14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000028000000}">
       <text>
         <r>
           <rPr>
@@ -2258,7 +2312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000027000000}">
+    <comment ref="O14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1800-000029000000}">
       <text>
         <r>
           <rPr>
@@ -2274,7 +2328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000028000000}">
+    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -2287,7 +2341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000029000000}">
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -2300,7 +2354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002A000000}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -2313,7 +2367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002B000000}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -2326,7 +2380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002C000000}">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -2339,7 +2393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002D000000}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002F000000}">
       <text>
         <r>
           <rPr>
@@ -2352,7 +2406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002E000000}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000030000000}">
       <text>
         <r>
           <rPr>
@@ -2365,7 +2419,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00002F000000}">
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000031000000}">
       <text>
         <r>
           <rPr>
@@ -2378,7 +2432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000030000000}">
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000032000000}">
       <text>
         <r>
           <rPr>
@@ -2391,7 +2445,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000031000000}">
+    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000033000000}">
       <text>
         <r>
           <rPr>
@@ -2404,7 +2458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000032000000}">
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000034000000}">
       <text>
         <r>
           <rPr>
@@ -2417,7 +2471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000033000000}">
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000035000000}">
       <text>
         <r>
           <rPr>
@@ -2430,7 +2484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000034000000}">
+    <comment ref="O18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000036000000}">
       <text>
         <r>
           <rPr>
@@ -2443,7 +2497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000035000000}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000037000000}">
       <text>
         <r>
           <rPr>
@@ -2456,7 +2510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000036000000}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000038000000}">
       <text>
         <r>
           <rPr>
@@ -2469,7 +2523,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000037000000}">
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000039000000}">
       <text>
         <r>
           <rPr>
@@ -2482,7 +2536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000038000000}">
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003A000000}">
       <text>
         <r>
           <rPr>
@@ -2495,7 +2549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000039000000}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003B000000}">
       <text>
         <r>
           <rPr>
@@ -2508,7 +2562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003A000000}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003C000000}">
       <text>
         <r>
           <rPr>
@@ -2521,7 +2575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003B000000}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003D000000}">
       <text>
         <r>
           <rPr>
@@ -2534,7 +2588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003C000000}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003E000000}">
       <text>
         <r>
           <rPr>
@@ -2547,7 +2601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003D000000}">
+    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003F000000}">
       <text>
         <r>
           <rPr>
@@ -2560,7 +2614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003E000000}">
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000040000000}">
       <text>
         <r>
           <rPr>
@@ -2573,7 +2627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00003F000000}">
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000041000000}">
       <text>
         <r>
           <rPr>
@@ -2586,7 +2640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000040000000}">
+    <comment ref="O20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000042000000}">
       <text>
         <r>
           <rPr>
@@ -2599,7 +2653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000041000000}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000043000000}">
       <text>
         <r>
           <rPr>
@@ -2612,7 +2666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000042000000}">
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000044000000}">
       <text>
         <r>
           <rPr>
@@ -2625,7 +2679,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000043000000}">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000045000000}">
       <text>
         <r>
           <rPr>
@@ -2634,11 +2688,39 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000044000000}">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000046000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000047000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000048000000}">
       <text>
         <r>
           <rPr>
@@ -2652,7 +2734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000045000000}">
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000049000000}">
       <text>
         <r>
           <rPr>
@@ -2666,7 +2748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000046000000}">
+    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -2680,7 +2762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000047000000}">
+    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -2694,7 +2776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000048000000}">
+    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -2707,7 +2789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000049000000}">
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -2720,7 +2802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004A000000}">
+    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004E000000}">
       <text>
         <r>
           <rPr>
@@ -2733,7 +2815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004B000000}">
+    <comment ref="O31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004F000000}">
       <text>
         <r>
           <rPr>
@@ -2746,7 +2828,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004C000000}">
+    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000050000000}">
       <text>
         <r>
           <rPr>
@@ -2759,7 +2841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004D000000}">
+    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000051000000}">
       <text>
         <r>
           <rPr>
@@ -2772,7 +2854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004E000000}">
+    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2785,7 +2867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00004F000000}">
+    <comment ref="O32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
       <text>
         <r>
           <rPr>
@@ -2798,7 +2880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000050000000}">
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
       <text>
         <r>
           <rPr>
@@ -2811,7 +2893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000051000000}">
+    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2824,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2837,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2850,7 +2932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2864,7 +2946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2878,7 +2960,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2892,7 +2974,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2906,7 +2988,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2920,7 +3002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2934,7 +3016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2948,7 +3030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2962,7 +3044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2976,7 +3058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2990,7 +3072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -3004,7 +3086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -3018,7 +3100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="O35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -3032,7 +3114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -3045,7 +3127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -3058,7 +3140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -3071,7 +3153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
       <text>
         <r>
           <rPr>
@@ -3084,7 +3166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
       <text>
         <r>
           <rPr>
@@ -3097,7 +3179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -3110,7 +3192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -3123,7 +3205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -3136,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -3149,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -3158,11 +3240,39 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -3176,7 +3286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -3190,7 +3300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -3204,7 +3314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -3218,7 +3328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -3232,7 +3342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -3246,7 +3356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -3260,7 +3370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -3274,7 +3384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -3288,7 +3398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -3302,7 +3412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -3316,7 +3426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -3330,7 +3440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -3344,7 +3454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -3358,7 +3468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -3372,7 +3482,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -3386,7 +3496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -3399,7 +3509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -3412,7 +3522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
       <text>
         <r>
           <rPr>
@@ -3425,7 +3535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
       <text>
         <r>
           <rPr>
@@ -3438,7 +3548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000085000000}">
       <text>
         <r>
           <rPr>
@@ -3451,7 +3561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000086000000}">
       <text>
         <r>
           <rPr>
@@ -3464,7 +3574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000087000000}">
       <text>
         <r>
           <rPr>
@@ -3477,7 +3587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000088000000}">
       <text>
         <r>
           <rPr>
@@ -3490,7 +3600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000089000000}">
       <text>
         <r>
           <rPr>
@@ -3503,7 +3613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008A000000}">
       <text>
         <r>
           <rPr>
@@ -3516,7 +3626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000085000000}">
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008B000000}">
       <text>
         <r>
           <rPr>
@@ -3529,7 +3639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000086000000}">
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008C000000}">
       <text>
         <r>
           <rPr>
@@ -3542,7 +3652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000087000000}">
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008D000000}">
       <text>
         <r>
           <rPr>
@@ -3556,7 +3666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000088000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008E000000}">
       <text>
         <r>
           <rPr>
@@ -3570,7 +3680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000089000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008F000000}">
       <text>
         <r>
           <rPr>
@@ -3584,7 +3694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008A000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000090000000}">
       <text>
         <r>
           <rPr>
@@ -3598,7 +3708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008B000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000091000000}">
       <text>
         <r>
           <rPr>
@@ -3612,7 +3722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008C000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000092000000}">
       <text>
         <r>
           <rPr>
@@ -3626,7 +3736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008D000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000093000000}">
       <text>
         <r>
           <rPr>
@@ -3640,7 +3750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008E000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000094000000}">
       <text>
         <r>
           <rPr>
@@ -3654,7 +3764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00008F000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000095000000}">
       <text>
         <r>
           <rPr>
@@ -3668,7 +3778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000090000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000096000000}">
       <text>
         <r>
           <rPr>
@@ -3682,7 +3792,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000091000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000097000000}">
       <text>
         <r>
           <rPr>
@@ -3696,7 +3806,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000092000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000098000000}">
       <text>
         <r>
           <rPr>
@@ -3710,7 +3820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000093000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000099000000}">
       <text>
         <r>
           <rPr>
@@ -3724,7 +3834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000094000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009A000000}">
       <text>
         <r>
           <rPr>
@@ -3737,7 +3847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000095000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009B000000}">
       <text>
         <r>
           <rPr>
@@ -3750,7 +3860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000096000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009C000000}">
       <text>
         <r>
           <rPr>
@@ -3763,7 +3873,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000097000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009D000000}">
       <text>
         <r>
           <rPr>
@@ -3776,7 +3886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000098000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009E000000}">
       <text>
         <r>
           <rPr>
@@ -3789,7 +3899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000099000000}">
+    <comment ref="E64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009F000000}">
       <text>
         <r>
           <rPr>
@@ -3802,7 +3912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009A000000}">
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-0000A0000000}">
       <text>
         <r>
           <rPr>
@@ -3815,7 +3925,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009B000000}">
+    <comment ref="E66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-0000A1000000}">
       <text>
         <r>
           <rPr>
@@ -3828,7 +3938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00009C000000}">
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-0000A2000000}">
       <text>
         <r>
           <rPr>
@@ -4502,7 +4612,77 @@
         </r>
       </text>
     </comment>
-    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000018000000}">
+    <comment ref="D28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -4515,7 +4695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000019000000}">
+    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -4528,7 +4708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001A000000}">
+    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -4541,7 +4721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001B000000}">
+    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000020000000}">
       <text>
         <r>
           <rPr>
@@ -4554,7 +4734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001C000000}">
+    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000021000000}">
       <text>
         <r>
           <rPr>
@@ -4567,7 +4747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001D000000}">
+    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000022000000}">
       <text>
         <r>
           <rPr>
@@ -4580,7 +4760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001E000000}">
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000023000000}">
       <text>
         <r>
           <rPr>
@@ -4593,7 +4773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00001F000000}">
+    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000024000000}">
       <text>
         <r>
           <rPr>
@@ -4606,7 +4786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000020000000}">
+    <comment ref="G44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000025000000}">
       <text>
         <r>
           <rPr>
@@ -4619,7 +4799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000021000000}">
+    <comment ref="H44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000026000000}">
       <text>
         <r>
           <rPr>
@@ -4632,7 +4812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000022000000}">
+    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000027000000}">
       <text>
         <r>
           <rPr>
@@ -4646,7 +4826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000023000000}">
+    <comment ref="E47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000028000000}">
       <text>
         <r>
           <rPr>
@@ -4660,7 +4840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000024000000}">
+    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000029000000}">
       <text>
         <r>
           <rPr>
@@ -4674,7 +4854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000025000000}">
+    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -4688,7 +4868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000026000000}">
+    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -4702,7 +4882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000027000000}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -4717,7 +4897,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000028000000}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -4732,7 +4912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000029000000}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -4747,7 +4927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002A000000}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002F000000}">
       <text>
         <r>
           <rPr>
@@ -4762,7 +4942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002B000000}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000030000000}">
       <text>
         <r>
           <rPr>
@@ -4777,7 +4957,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002C000000}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000031000000}">
       <text>
         <r>
           <rPr>
@@ -4791,7 +4971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002D000000}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000032000000}">
       <text>
         <r>
           <rPr>
@@ -4805,7 +4985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002E000000}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000033000000}">
       <text>
         <r>
           <rPr>
@@ -4819,7 +4999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00002F000000}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000034000000}">
       <text>
         <r>
           <rPr>
@@ -4833,7 +5013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000030000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000035000000}">
       <text>
         <r>
           <rPr>
@@ -4847,7 +5027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000031000000}">
+    <comment ref="D53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000036000000}">
       <text>
         <r>
           <rPr>
@@ -4860,7 +5040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000032000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000037000000}">
       <text>
         <r>
           <rPr>
@@ -4873,7 +5053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000033000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000038000000}">
       <text>
         <r>
           <rPr>
@@ -4886,7 +5066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000034000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000039000000}">
       <text>
         <r>
           <rPr>
@@ -4899,7 +5079,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000035000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003A000000}">
       <text>
         <r>
           <rPr>
@@ -4912,7 +5092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000036000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003B000000}">
       <text>
         <r>
           <rPr>
@@ -4925,7 +5105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000037000000}">
+    <comment ref="H59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003C000000}">
       <text>
         <r>
           <rPr>
@@ -4938,7 +5118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000038000000}">
+    <comment ref="F61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003D000000}">
       <text>
         <r>
           <rPr>
@@ -4951,7 +5131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000039000000}">
+    <comment ref="G61" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003E000000}">
       <text>
         <r>
           <rPr>
@@ -4964,7 +5144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003A000000}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003F000000}">
       <text>
         <r>
           <rPr>
@@ -4977,7 +5157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003B000000}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000040000000}">
       <text>
         <r>
           <rPr>
@@ -4990,7 +5170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003C000000}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000041000000}">
       <text>
         <r>
           <rPr>
@@ -5003,7 +5183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003D000000}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000042000000}">
       <text>
         <r>
           <rPr>
@@ -5016,7 +5196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003E000000}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000043000000}">
       <text>
         <r>
           <rPr>
@@ -5029,7 +5209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00003F000000}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000044000000}">
       <text>
         <r>
           <rPr>
@@ -5042,7 +5222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000040000000}">
+    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000045000000}">
       <text>
         <r>
           <rPr>
@@ -5055,7 +5235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000041000000}">
+    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000046000000}">
       <text>
         <r>
           <rPr>
@@ -5068,7 +5248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000042000000}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000047000000}">
       <text>
         <r>
           <rPr>
@@ -5081,7 +5261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000043000000}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000048000000}">
       <text>
         <r>
           <rPr>
@@ -5094,7 +5274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000044000000}">
+    <comment ref="F73" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000049000000}">
       <text>
         <r>
           <rPr>
@@ -5108,7 +5288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F75" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000045000000}">
+    <comment ref="F75" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -5122,7 +5302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000046000000}">
+    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -5136,7 +5316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000047000000}">
+    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -5150,7 +5330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000048000000}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -5164,7 +5344,77 @@
         </r>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000049000000}">
+    <comment ref="D83" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E83" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F83" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000050000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G83" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000051000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H83" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000052000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000053000000}">
       <text>
         <r>
           <rPr>
@@ -5177,7 +5427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004A000000}">
+    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000054000000}">
       <text>
         <r>
           <rPr>
@@ -5190,7 +5440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004B000000}">
+    <comment ref="F99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000055000000}">
       <text>
         <r>
           <rPr>
@@ -5203,7 +5453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004C000000}">
+    <comment ref="G99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000056000000}">
       <text>
         <r>
           <rPr>
@@ -5216,7 +5466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004D000000}">
+    <comment ref="H99" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000057000000}">
       <text>
         <r>
           <rPr>
@@ -5229,7 +5479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004E000000}">
+    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000058000000}">
       <text>
         <r>
           <rPr>
@@ -5243,7 +5493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00004F000000}">
+    <comment ref="E102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000059000000}">
       <text>
         <r>
           <rPr>
@@ -5257,7 +5507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000050000000}">
+    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -5271,7 +5521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000051000000}">
+    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -5285,7 +5535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000052000000}">
+    <comment ref="H102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -5299,7 +5549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000053000000}">
+    <comment ref="D104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -5314,7 +5564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000054000000}">
+    <comment ref="E104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -5329,7 +5579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000055000000}">
+    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -5344,7 +5594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000056000000}">
+    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000060000000}">
       <text>
         <r>
           <rPr>
@@ -5359,7 +5609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000057000000}">
+    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000061000000}">
       <text>
         <r>
           <rPr>
@@ -5374,7 +5624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000058000000}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000062000000}">
       <text>
         <r>
           <rPr>
@@ -5388,7 +5638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000059000000}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000063000000}">
       <text>
         <r>
           <rPr>
@@ -5402,7 +5652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005A000000}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000064000000}">
       <text>
         <r>
           <rPr>
@@ -5416,7 +5666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005B000000}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000065000000}">
       <text>
         <r>
           <rPr>
@@ -5430,7 +5680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005C000000}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000066000000}">
       <text>
         <r>
           <rPr>
@@ -5444,7 +5694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005D000000}">
+    <comment ref="D108" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000067000000}">
       <text>
         <r>
           <rPr>
@@ -5457,7 +5707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005E000000}">
+    <comment ref="F113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000068000000}">
       <text>
         <r>
           <rPr>
@@ -5470,7 +5720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00005F000000}">
+    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000069000000}">
       <text>
         <r>
           <rPr>
@@ -5483,7 +5733,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000060000000}">
+    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -5496,7 +5746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000061000000}">
+    <comment ref="F114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -5509,7 +5759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000062000000}">
+    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -5522,7 +5772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000063000000}">
+    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -5535,7 +5785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000064000000}">
+    <comment ref="F116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -5548,7 +5798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000065000000}">
+    <comment ref="G116" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -5561,7 +5811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000066000000}">
+    <comment ref="F118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000070000000}">
       <text>
         <r>
           <rPr>
@@ -5574,7 +5824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000067000000}">
+    <comment ref="G118" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000071000000}">
       <text>
         <r>
           <rPr>
@@ -5587,7 +5837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000068000000}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000072000000}">
       <text>
         <r>
           <rPr>
@@ -5600,7 +5850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000069000000}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000073000000}">
       <text>
         <r>
           <rPr>
@@ -5613,7 +5863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006A000000}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000074000000}">
       <text>
         <r>
           <rPr>
@@ -5626,7 +5876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006B000000}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000075000000}">
       <text>
         <r>
           <rPr>
@@ -5639,7 +5889,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006C000000}">
+    <comment ref="F124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000076000000}">
       <text>
         <r>
           <rPr>
@@ -5652,7 +5902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006D000000}">
+    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000077000000}">
       <text>
         <r>
           <rPr>
@@ -5665,7 +5915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006E000000}">
+    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000078000000}">
       <text>
         <r>
           <rPr>
@@ -5678,7 +5928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00006F000000}">
+    <comment ref="G126" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000079000000}">
       <text>
         <r>
           <rPr>
@@ -5691,7 +5941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000070000000}">
+    <comment ref="F128" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -5705,7 +5955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000071000000}">
+    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -5719,7 +5969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000072000000}">
+    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -5733,7 +5983,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000073000000}">
+    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -5747,7 +5997,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000074000000}">
+    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -5761,7 +6011,77 @@
         </r>
       </text>
     </comment>
-    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000075000000}">
+    <comment ref="D138" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E138" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000080000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F138" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000081000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G138" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000082000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H138" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000083000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000084000000}">
       <text>
         <r>
           <rPr>
@@ -5774,7 +6094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000076000000}">
+    <comment ref="E154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000085000000}">
       <text>
         <r>
           <rPr>
@@ -5787,7 +6107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000077000000}">
+    <comment ref="F154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000086000000}">
       <text>
         <r>
           <rPr>
@@ -5800,7 +6120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000078000000}">
+    <comment ref="G154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000087000000}">
       <text>
         <r>
           <rPr>
@@ -5813,7 +6133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000079000000}">
+    <comment ref="H154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000088000000}">
       <text>
         <r>
           <rPr>
@@ -5826,7 +6146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007A000000}">
+    <comment ref="D157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000089000000}">
       <text>
         <r>
           <rPr>
@@ -5840,7 +6160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007B000000}">
+    <comment ref="E157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008A000000}">
       <text>
         <r>
           <rPr>
@@ -5854,7 +6174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007C000000}">
+    <comment ref="F157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008B000000}">
       <text>
         <r>
           <rPr>
@@ -5868,7 +6188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007D000000}">
+    <comment ref="G157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008C000000}">
       <text>
         <r>
           <rPr>
@@ -5882,7 +6202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007E000000}">
+    <comment ref="H157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008D000000}">
       <text>
         <r>
           <rPr>
@@ -5896,7 +6216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00007F000000}">
+    <comment ref="D159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008E000000}">
       <text>
         <r>
           <rPr>
@@ -5911,7 +6231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000080000000}">
+    <comment ref="E159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-00008F000000}">
       <text>
         <r>
           <rPr>
@@ -5926,7 +6246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000081000000}">
+    <comment ref="F159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000090000000}">
       <text>
         <r>
           <rPr>
@@ -5941,7 +6261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000082000000}">
+    <comment ref="G159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000091000000}">
       <text>
         <r>
           <rPr>
@@ -5956,7 +6276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000083000000}">
+    <comment ref="H159" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000092000000}">
       <text>
         <r>
           <rPr>
@@ -5971,7 +6291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000084000000}">
+    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000093000000}">
       <text>
         <r>
           <rPr>
@@ -5985,7 +6305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000085000000}">
+    <comment ref="E161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000094000000}">
       <text>
         <r>
           <rPr>
@@ -5999,7 +6319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000086000000}">
+    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000095000000}">
       <text>
         <r>
           <rPr>
@@ -6013,7 +6333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000087000000}">
+    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000096000000}">
       <text>
         <r>
           <rPr>
@@ -6027,7 +6347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000088000000}">
+    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000097000000}">
       <text>
         <r>
           <rPr>
@@ -6041,7 +6361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000089000000}">
+    <comment ref="D163" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000098000000}">
       <text>
         <r>
           <rPr>
@@ -6061,10 +6381,24 @@
 <file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Nick Scott</author>
     <author>Tharindu Wickramaarachchi</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000001000000}">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Nick Scott:
+Note: Ca supplementation impacts preterm birth, not curretly captured in the model Hofmeyr et al 2023, RR 0.76 (0.60-0.97), all women</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -6078,7 +6412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000002000000}">
+    <comment ref="E3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000003000000}">
       <text>
         <r>
           <rPr>
@@ -6092,7 +6426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000003000000}">
+    <comment ref="F3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000004000000}">
       <text>
         <r>
           <rPr>
@@ -6106,7 +6440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000004000000}">
+    <comment ref="G3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000005000000}">
       <text>
         <r>
           <rPr>
@@ -6120,7 +6454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000005000000}">
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000006000000}">
       <text>
         <r>
           <rPr>
@@ -6134,7 +6468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000006000000}">
+    <comment ref="E5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000007000000}">
       <text>
         <r>
           <rPr>
@@ -6148,7 +6482,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000007000000}">
+    <comment ref="F5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000008000000}">
       <text>
         <r>
           <rPr>
@@ -6162,7 +6496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000008000000}">
+    <comment ref="G5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000009000000}">
       <text>
         <r>
           <rPr>
@@ -6176,7 +6510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000009000000}">
+    <comment ref="D7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -6190,7 +6524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000A000000}">
+    <comment ref="E7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -6204,7 +6538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000B000000}">
+    <comment ref="F7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -6218,7 +6552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000C000000}">
+    <comment ref="G7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -6232,7 +6566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000D000000}">
+    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -6246,7 +6580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000E000000}">
+    <comment ref="E12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -6260,7 +6594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-00000F000000}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000010000000}">
       <text>
         <r>
           <rPr>
@@ -6274,7 +6608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000010000000}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000011000000}">
       <text>
         <r>
           <rPr>
@@ -6288,7 +6622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000011000000}">
+    <comment ref="D21" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000012000000}">
       <text>
         <r>
           <rPr>
@@ -6302,7 +6636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000012000000}">
+    <comment ref="E21" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000013000000}">
       <text>
         <r>
           <rPr>
@@ -6316,7 +6650,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000013000000}">
+    <comment ref="F21" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000014000000}">
       <text>
         <r>
           <rPr>
@@ -6330,7 +6664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000014000000}">
+    <comment ref="G21" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000015000000}">
       <text>
         <r>
           <rPr>
@@ -7306,8 +7640,8 @@
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Nick Scott</author>
     <author>Tharindu Wickramaarachchi</author>
-    <author>Nick Scott</author>
   </authors>
   <commentList>
     <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000001000000}">
@@ -7318,8 +7652,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
         </r>
       </text>
     </comment>
@@ -7331,8 +7665,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
         </r>
       </text>
     </comment>
@@ -7344,8 +7678,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t xml:space="preserve">Nick Scott:
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
         </r>
       </text>
     </comment>
@@ -7357,8 +7691,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t xml:space="preserve">Nick Scott:
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
         </r>
       </text>
     </comment>
@@ -7370,8 +7704,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7383,8 +7717,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7396,8 +7730,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7409,12 +7743,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000009000000}">
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -7428,7 +7762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000A000000}">
+    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -7442,7 +7776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000B000000}">
+    <comment ref="G31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -7456,7 +7790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000C000000}">
+    <comment ref="G32" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -7470,7 +7804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A36" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000D000000}">
+    <comment ref="A36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -7491,8 +7825,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
         </r>
       </text>
     </comment>
@@ -7504,8 +7838,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
         </r>
       </text>
     </comment>
@@ -7517,8 +7851,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t xml:space="preserve">Nick Scott:
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
         </r>
       </text>
     </comment>
@@ -7530,8 +7864,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t xml:space="preserve">Nick Scott:
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
         </r>
       </text>
     </comment>
@@ -7543,8 +7877,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7556,8 +7890,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7569,8 +7903,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7582,12 +7916,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A89" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
       <text>
         <r>
           <rPr>
@@ -7608,8 +7942,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
         </r>
       </text>
     </comment>
@@ -7621,8 +7955,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
         </r>
       </text>
     </comment>
@@ -7634,8 +7968,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t xml:space="preserve">Nick Scott:
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
         </r>
       </text>
     </comment>
@@ -7647,8 +7981,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t xml:space="preserve">Nick Scott:
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
         </r>
       </text>
     </comment>
@@ -7660,8 +7994,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7673,8 +8007,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7686,8 +8020,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
         </r>
       </text>
     </comment>
@@ -7699,12 +8033,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t xml:space="preserve">Tharindu Wickramaarachchi:
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A125" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00001F000000}">
+          <t>Nick Scott:
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A125" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -7717,7 +8051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A142" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000020000000}">
+    <comment ref="A142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000020000000}">
       <text>
         <r>
           <rPr>
@@ -7735,7 +8069,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="341">
   <si>
     <t>Baseline year data</t>
   </si>
@@ -10170,7 +10504,7 @@
         <v>0.95</v>
       </c>
       <c r="D2" s="56">
-        <v>36.11916955958214</v>
+        <v>144.3361538195548</v>
       </c>
       <c r="E2" s="56" t="s">
         <v>167</v>
@@ -10193,7 +10527,7 @@
         <v>0.95</v>
       </c>
       <c r="D3" s="56">
-        <v>42.481123974359448</v>
+        <v>19.75203299904819</v>
       </c>
       <c r="E3" s="56" t="s">
         <v>167</v>
@@ -10216,7 +10550,7 @@
         <v>0.95</v>
       </c>
       <c r="D4" s="56">
-        <v>70.900000000000006</v>
+        <v>16.029464016122279</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>167</v>
@@ -10285,7 +10619,7 @@
         <v>0.95</v>
       </c>
       <c r="D7" s="56">
-        <v>99.99</v>
+        <v>0.19283527130965261</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>167</v>
@@ -10308,7 +10642,7 @@
         <v>0.95</v>
       </c>
       <c r="D8" s="56">
-        <v>99.99</v>
+        <v>0.10284547803181469</v>
       </c>
       <c r="E8" s="56" t="s">
         <v>167</v>
@@ -10331,7 +10665,7 @@
         <v>0.95</v>
       </c>
       <c r="D9" s="56">
-        <v>99.99</v>
+        <v>0.21140459373206369</v>
       </c>
       <c r="E9" s="56" t="s">
         <v>167</v>
@@ -10492,7 +10826,7 @@
         <v>0.95</v>
       </c>
       <c r="D16" s="56">
-        <v>0.2380786122301152</v>
+        <v>5.5080133892626542</v>
       </c>
       <c r="E16" s="56" t="s">
         <v>167</v>
@@ -10538,7 +10872,7 @@
         <v>0.95</v>
       </c>
       <c r="D18" s="56">
-        <v>1.73788639265208</v>
+        <v>16.029464016122279</v>
       </c>
       <c r="E18" s="56" t="s">
         <v>167</v>
@@ -10561,7 +10895,7 @@
         <v>0.95</v>
       </c>
       <c r="D19" s="56">
-        <v>1.73788639265208</v>
+        <v>16.029464016122279</v>
       </c>
       <c r="E19" s="56" t="s">
         <v>167</v>
@@ -10607,7 +10941,7 @@
         <v>0.95</v>
       </c>
       <c r="D21" s="56">
-        <v>11.875561895445459</v>
+        <v>16.46619599914094</v>
       </c>
       <c r="E21" s="56" t="s">
         <v>167</v>
@@ -10722,7 +11056,7 @@
         <v>0.95</v>
       </c>
       <c r="D26" s="56">
-        <v>99.99</v>
+        <v>7.6264796156856711</v>
       </c>
       <c r="E26" s="56" t="s">
         <v>167</v>
@@ -10745,7 +11079,7 @@
         <v>0.95</v>
       </c>
       <c r="D27" s="56">
-        <v>19.49524523887251</v>
+        <v>30.36727751762248</v>
       </c>
       <c r="E27" s="56" t="s">
         <v>167</v>
@@ -10791,7 +11125,7 @@
         <v>0.95</v>
       </c>
       <c r="D29" s="56">
-        <v>63.641193459852339</v>
+        <v>193.6128732031849</v>
       </c>
       <c r="E29" s="56" t="s">
         <v>167</v>
@@ -10837,7 +11171,7 @@
         <v>0.95</v>
       </c>
       <c r="D31" s="56">
-        <v>4.5094624774474914</v>
+        <v>398.07273654067848</v>
       </c>
       <c r="E31" s="56" t="s">
         <v>167</v>
@@ -10860,7 +11194,7 @@
         <v>0.95</v>
       </c>
       <c r="D32" s="56">
-        <v>0.45591617905202908</v>
+        <v>1.4358697255793671</v>
       </c>
       <c r="E32" s="56" t="s">
         <v>167</v>
@@ -10998,7 +11332,7 @@
         <v>0.95</v>
       </c>
       <c r="D38" s="56">
-        <v>2.7969611357764639</v>
+        <v>5.3874863984233787</v>
       </c>
       <c r="E38" s="56" t="s">
         <v>167</v>
@@ -11021,7 +11355,7 @@
         <v>0.95</v>
       </c>
       <c r="D39" s="56">
-        <v>99.99</v>
+        <v>7.541139000710408</v>
       </c>
       <c r="E39" s="56" t="s">
         <v>167</v>
@@ -11131,12 +11465,8 @@
       <c r="C8" s="58"/>
     </row>
     <row r="9" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>192</v>
-      </c>
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="58"/>
     </row>
     <row r="10" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11174,22 +11504,22 @@
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="59"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="59"/>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="58"/>
       <c r="C20" s="58"/>
@@ -11283,13 +11613,13 @@
     <row r="16" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
   </sheetData>
@@ -15531,7 +15861,7 @@
       <c r="J16" s="87"/>
       <c r="K16" s="87"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>182</v>
       </c>
@@ -15548,7 +15878,7 @@
       <c r="J17" s="87"/>
       <c r="K17" s="87"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>148</v>
       </c>
@@ -15567,7 +15897,7 @@
       <c r="J18" s="87"/>
       <c r="K18" s="87"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>151</v>
       </c>
@@ -15586,7 +15916,7 @@
       <c r="J19" s="87"/>
       <c r="K19" s="87"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>152</v>
       </c>
@@ -15605,7 +15935,7 @@
       <c r="J20" s="87"/>
       <c r="K20" s="87"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>183</v>
       </c>
@@ -17311,7 +17641,7 @@
         <v>145</v>
       </c>
       <c r="D5" s="88">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E5" s="88">
         <v>1</v>
@@ -17332,7 +17662,7 @@
         <v>146</v>
       </c>
       <c r="D6" s="88">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E6" s="88">
         <v>1</v>
@@ -17379,7 +17709,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="88">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F8" s="88">
         <v>1</v>
@@ -17400,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="88">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F9" s="88">
         <v>1</v>
@@ -17447,7 +17777,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="88">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G11" s="88">
         <v>1</v>
@@ -17468,7 +17798,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="88">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G12" s="88">
         <v>1</v>
@@ -17515,7 +17845,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="88">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H14" s="88">
         <v>1</v>
@@ -17536,7 +17866,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="88">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H15" s="88">
         <v>1</v>
@@ -17619,7 +17949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="104"/>
       <c r="C20" s="8" t="s">
         <v>146</v>
@@ -17640,7 +17970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="104"/>
       <c r="C21" s="8" t="s">
         <v>147</v>
@@ -17661,7 +17991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>67</v>
       </c>
@@ -17684,7 +18014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="104"/>
       <c r="C23" s="8" t="s">
         <v>146</v>
@@ -17705,7 +18035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="104"/>
       <c r="C24" s="8" t="s">
         <v>147</v>
@@ -17726,7 +18056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>77</v>
       </c>
@@ -17749,7 +18079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="104"/>
       <c r="C26" s="8" t="s">
         <v>146</v>
@@ -17770,7 +18100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="104"/>
       <c r="C27" s="8" t="s">
         <v>147</v>
@@ -17791,7 +18121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="103" t="s">
         <v>78</v>
       </c>
@@ -17814,7 +18144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="104"/>
       <c r="C29" s="8" t="s">
         <v>146</v>
@@ -17835,7 +18165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="104"/>
       <c r="C30" s="8" t="s">
         <v>147</v>
@@ -17856,7 +18186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="103" t="s">
         <v>79</v>
       </c>
@@ -17879,7 +18209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="104"/>
       <c r="C32" s="8" t="s">
         <v>146</v>
@@ -17900,7 +18230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="104"/>
       <c r="C33" s="8" t="s">
         <v>147</v>
@@ -17944,7 +18274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="86"/>
       <c r="E35" s="86"/>
       <c r="F35" s="86"/>
@@ -17977,7 +18307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="104"/>
       <c r="C37" s="8" t="s">
         <v>146</v>
@@ -17998,7 +18328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="104"/>
       <c r="C38" s="8" t="s">
         <v>147</v>
@@ -18019,7 +18349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="103" t="s">
         <v>67</v>
       </c>
@@ -18042,7 +18372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="104"/>
       <c r="C40" s="8" t="s">
         <v>146</v>
@@ -18063,7 +18393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="104"/>
       <c r="C41" s="8" t="s">
         <v>147</v>
@@ -18084,7 +18414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="103" t="s">
         <v>77</v>
       </c>
@@ -18107,7 +18437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="104"/>
       <c r="C43" s="8" t="s">
         <v>146</v>
@@ -18128,7 +18458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="104"/>
       <c r="C44" s="8" t="s">
         <v>147</v>
@@ -18149,7 +18479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="103" t="s">
         <v>78</v>
       </c>
@@ -18172,7 +18502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="104"/>
       <c r="C46" s="8" t="s">
         <v>146</v>
@@ -18193,7 +18523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="104"/>
       <c r="C47" s="8" t="s">
         <v>147</v>
@@ -18214,7 +18544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="103" t="s">
         <v>79</v>
       </c>
@@ -18237,7 +18567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="104"/>
       <c r="C49" s="8" t="s">
         <v>146</v>
@@ -18258,7 +18588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="104"/>
       <c r="C50" s="8" t="s">
         <v>147</v>
@@ -18371,7 +18701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="104"/>
       <c r="C56" s="8" t="s">
         <v>146</v>
@@ -18397,7 +18727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="104"/>
       <c r="C57" s="8" t="s">
         <v>147</v>
@@ -18423,7 +18753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="103" t="s">
         <v>67</v>
       </c>
@@ -18431,7 +18761,7 @@
         <v>145</v>
       </c>
       <c r="D58" s="88">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E58" s="88">
         <f t="shared" ref="E58:H60" si="1">IF(E5=1,1,E5*0.9)</f>
@@ -18450,13 +18780,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="104"/>
       <c r="C59" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D59" s="88">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E59" s="88">
         <f t="shared" si="1"/>
@@ -18475,7 +18805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="104"/>
       <c r="C60" s="8" t="s">
         <v>147</v>
@@ -18501,7 +18831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="103" t="s">
         <v>77</v>
       </c>
@@ -18513,7 +18843,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="88">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F61" s="88">
         <f t="shared" ref="F61:H63" si="3">IF(F8=1,1,F8*0.9)</f>
@@ -18528,7 +18858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="104"/>
       <c r="C62" s="8" t="s">
         <v>146</v>
@@ -18538,7 +18868,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="88">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F62" s="88">
         <f t="shared" si="3"/>
@@ -18553,7 +18883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="104"/>
       <c r="C63" s="8" t="s">
         <v>147</v>
@@ -18579,7 +18909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="103" t="s">
         <v>78</v>
       </c>
@@ -18595,7 +18925,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="88">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G64" s="88">
         <f t="shared" ref="G64:H66" si="5">IF(G11=1,1,G11*0.9)</f>
@@ -18606,7 +18936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="104"/>
       <c r="C65" s="8" t="s">
         <v>146</v>
@@ -18620,7 +18950,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="88">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G65" s="88">
         <f t="shared" si="5"/>
@@ -18631,7 +18961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="104"/>
       <c r="C66" s="8" t="s">
         <v>147</v>
@@ -18657,7 +18987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="103" t="s">
         <v>79</v>
       </c>
@@ -18677,14 +19007,14 @@
         <v>1</v>
       </c>
       <c r="G67" s="88">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H67" s="88">
         <f>IF(H14=1,1,H14*0.9)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="104"/>
       <c r="C68" s="8" t="s">
         <v>146</v>
@@ -18702,14 +19032,14 @@
         <v>1</v>
       </c>
       <c r="G68" s="88">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H68" s="88">
         <f>IF(H15=1,1,H15*0.9)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="104"/>
       <c r="C69" s="8" t="s">
         <v>147</v>
@@ -18763,7 +19093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="86"/>
       <c r="E71" s="86"/>
       <c r="F71" s="86"/>
@@ -18801,7 +19131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="104"/>
       <c r="C73" s="8" t="s">
         <v>146</v>
@@ -18827,7 +19157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="104"/>
       <c r="C74" s="8" t="s">
         <v>147</v>
@@ -18853,7 +19183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="103" t="s">
         <v>67</v>
       </c>
@@ -18881,7 +19211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="104"/>
       <c r="C76" s="8" t="s">
         <v>146</v>
@@ -18907,7 +19237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="104"/>
       <c r="C77" s="8" t="s">
         <v>147</v>
@@ -18933,7 +19263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="103" t="s">
         <v>77</v>
       </c>
@@ -18961,7 +19291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="104"/>
       <c r="C79" s="8" t="s">
         <v>146</v>
@@ -18987,7 +19317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="104"/>
       <c r="C80" s="8" t="s">
         <v>147</v>
@@ -19013,7 +19343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="103" t="s">
         <v>78</v>
       </c>
@@ -19041,7 +19371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="104"/>
       <c r="C82" s="8" t="s">
         <v>146</v>
@@ -19067,7 +19397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="104"/>
       <c r="C83" s="8" t="s">
         <v>147</v>
@@ -19093,7 +19423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="103" t="s">
         <v>79</v>
       </c>
@@ -19121,7 +19451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="104"/>
       <c r="C85" s="8" t="s">
         <v>146</v>
@@ -19147,7 +19477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="104"/>
       <c r="C86" s="8" t="s">
         <v>147</v>
@@ -19201,7 +19531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="86"/>
       <c r="E88" s="86"/>
       <c r="F88" s="86"/>
@@ -19239,7 +19569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="104"/>
       <c r="C90" s="8" t="s">
         <v>146</v>
@@ -19265,7 +19595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="104"/>
       <c r="C91" s="8" t="s">
         <v>147</v>
@@ -19291,7 +19621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="103" t="s">
         <v>67</v>
       </c>
@@ -19319,7 +19649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="104"/>
       <c r="C93" s="8" t="s">
         <v>146</v>
@@ -19345,7 +19675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="104"/>
       <c r="C94" s="8" t="s">
         <v>147</v>
@@ -19371,7 +19701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="103" t="s">
         <v>77</v>
       </c>
@@ -19399,7 +19729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="104"/>
       <c r="C96" s="8" t="s">
         <v>146</v>
@@ -19425,7 +19755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="104"/>
       <c r="C97" s="8" t="s">
         <v>147</v>
@@ -19451,7 +19781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="103" t="s">
         <v>78</v>
       </c>
@@ -19479,7 +19809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="104"/>
       <c r="C99" s="8" t="s">
         <v>146</v>
@@ -19505,7 +19835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="104"/>
       <c r="C100" s="8" t="s">
         <v>147</v>
@@ -19531,7 +19861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="103" t="s">
         <v>79</v>
       </c>
@@ -19559,7 +19889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="104"/>
       <c r="C102" s="8" t="s">
         <v>146</v>
@@ -19585,7 +19915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="104"/>
       <c r="C103" s="8" t="s">
         <v>147</v>
@@ -19708,7 +20038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="104"/>
       <c r="C109" s="8" t="s">
         <v>146</v>
@@ -19734,7 +20064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="104"/>
       <c r="C110" s="8" t="s">
         <v>147</v>
@@ -19760,7 +20090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="103" t="s">
         <v>67</v>
       </c>
@@ -19768,10 +20098,10 @@
         <v>145</v>
       </c>
       <c r="D111" s="88">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E111" s="88">
-        <f t="shared" ref="E111:H113" si="11">IF(E5=1,1,E5*1.05)</f>
+        <f t="shared" ref="E111:G113" si="11">IF(E58=1,1,E58*0.9)</f>
         <v>1</v>
       </c>
       <c r="F111" s="88">
@@ -19783,17 +20113,17 @@
         <v>1</v>
       </c>
       <c r="H111" s="88">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H111:H123" si="12">IF(H5=1,1,H5*1.05)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="104"/>
       <c r="C112" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D112" s="88">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E112" s="88">
         <f t="shared" si="11"/>
@@ -19808,17 +20138,17 @@
         <v>1</v>
       </c>
       <c r="H112" s="88">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="104"/>
       <c r="C113" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D113" s="88">
-        <f t="shared" ref="D113:D123" si="12">IF(D7=1,1,D7*1.05)</f>
+        <f t="shared" ref="D113:D121" si="13">IF(D60=1,1,D60*0.9)</f>
         <v>1</v>
       </c>
       <c r="E113" s="88">
@@ -19834,11 +20164,11 @@
         <v>1</v>
       </c>
       <c r="H113" s="88">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="103" t="s">
         <v>77</v>
       </c>
@@ -19846,77 +20176,77 @@
         <v>145</v>
       </c>
       <c r="D114" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E114" s="88">
+        <v>3.09</v>
+      </c>
+      <c r="F114" s="88">
+        <f t="shared" ref="F114:G116" si="14">IF(F61=1,1,F61*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="G114" s="88">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="H114" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E114" s="88">
-        <v>2.11</v>
-      </c>
-      <c r="F114" s="88">
-        <f t="shared" ref="F114:H116" si="13">IF(F8=1,1,F8*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="G114" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="H114" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="104"/>
       <c r="C115" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D115" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E115" s="88">
+        <v>3.09</v>
+      </c>
+      <c r="F115" s="88">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G115" s="88">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="H115" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E115" s="88">
-        <v>2.11</v>
-      </c>
-      <c r="F115" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="G115" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="H115" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="104"/>
       <c r="C116" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D116" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E116" s="88">
+        <f t="shared" ref="E116:E121" si="15">IF(E63=1,1,E63*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="F116" s="88">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G116" s="88">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="H116" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E116" s="88">
-        <f t="shared" ref="E116:E123" si="14">IF(E10=1,1,E10*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="F116" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="G116" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="H116" s="88">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="103" t="s">
         <v>78</v>
       </c>
@@ -19924,77 +20254,77 @@
         <v>145</v>
       </c>
       <c r="D117" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E117" s="88">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="F117" s="88">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G117" s="88">
+        <f>IF(G64=1,1,G64*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="H117" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E117" s="88">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F117" s="88">
-        <v>2.11</v>
-      </c>
-      <c r="G117" s="88">
-        <f t="shared" ref="G117:H119" si="15">IF(G11=1,1,G11*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="H117" s="88">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="104"/>
       <c r="C118" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D118" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E118" s="88">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="F118" s="88">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G118" s="88">
+        <f>IF(G65=1,1,G65*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="H118" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E118" s="88">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F118" s="88">
-        <v>2.11</v>
-      </c>
-      <c r="G118" s="88">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="H118" s="88">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="104"/>
       <c r="C119" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D119" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E119" s="88">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="F119" s="88">
+        <f>IF(F66=1,1,F66*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="G119" s="88">
+        <f>IF(G66=1,1,G66*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="H119" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E119" s="88">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F119" s="88">
-        <f>IF(F13=1,1,F13*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="G119" s="88">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="H119" s="88">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="103" t="s">
         <v>79</v>
       </c>
@@ -20002,73 +20332,73 @@
         <v>145</v>
       </c>
       <c r="D120" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E120" s="88">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="F120" s="88">
+        <f>IF(F67=1,1,F67*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="G120" s="88">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H120" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E120" s="88">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F120" s="88">
-        <f>IF(F14=1,1,F14*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="G120" s="88">
-        <v>2.11</v>
-      </c>
-      <c r="H120" s="88">
-        <f>IF(H14=1,1,H14*1.05)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="104"/>
       <c r="C121" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D121" s="88">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E121" s="88">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="F121" s="88">
+        <f>IF(F68=1,1,F68*0.9)</f>
+        <v>1</v>
+      </c>
+      <c r="G121" s="88">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H121" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="E121" s="88">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F121" s="88">
-        <f>IF(F15=1,1,F15*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="G121" s="88">
-        <v>2.11</v>
-      </c>
-      <c r="H121" s="88">
-        <f>IF(H15=1,1,H15*1.05)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="104"/>
       <c r="C122" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D122" s="88">
+        <f t="shared" ref="D122:G123" si="16">IF(D16=1,1,D16*1.05)</f>
+        <v>1</v>
+      </c>
+      <c r="E122" s="88">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="F122" s="88">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="G122" s="88">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="H122" s="88">
         <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="E122" s="88">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F122" s="88">
-        <f>IF(F16=1,1,F16*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="G122" s="88">
-        <f>IF(G16=1,1,G16*1.05)</f>
-        <v>1</v>
-      </c>
-      <c r="H122" s="88">
-        <f>IF(H16=1,1,H16*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -20080,27 +20410,27 @@
         <v>147</v>
       </c>
       <c r="D123" s="88">
+        <f t="shared" si="16"/>
+        <v>1.1025</v>
+      </c>
+      <c r="E123" s="88">
+        <f t="shared" si="16"/>
+        <v>1.1025</v>
+      </c>
+      <c r="F123" s="88">
+        <f t="shared" si="16"/>
+        <v>1.1025</v>
+      </c>
+      <c r="G123" s="88">
+        <f t="shared" si="16"/>
+        <v>1.1025</v>
+      </c>
+      <c r="H123" s="88">
         <f t="shared" si="12"/>
-        <v>1.1025</v>
-      </c>
-      <c r="E123" s="88">
-        <f t="shared" si="14"/>
-        <v>1.1025</v>
-      </c>
-      <c r="F123" s="88">
-        <f>IF(F17=1,1,F17*1.05)</f>
-        <v>1.1025</v>
-      </c>
-      <c r="G123" s="88">
-        <f>IF(G17=1,1,G17*1.05)</f>
-        <v>1.1025</v>
-      </c>
-      <c r="H123" s="88">
-        <f>IF(H17=1,1,H17*1.05)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="86"/>
       <c r="E124" s="86"/>
       <c r="F124" s="86"/>
@@ -20118,79 +20448,79 @@
         <v>145</v>
       </c>
       <c r="D125" s="88">
-        <f t="shared" ref="D125:H134" si="16">IF(D19=1,1,D19*1.05)</f>
+        <f t="shared" ref="D125:H134" si="17">IF(D19=1,1,D19*1.05)</f>
         <v>1</v>
       </c>
       <c r="E125" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F125" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G125" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H125" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="104"/>
       <c r="C126" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D126" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E126" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F126" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G126" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H126" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="104"/>
       <c r="C127" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D127" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E127" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F127" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G127" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H127" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="103" t="s">
         <v>67</v>
       </c>
@@ -20198,79 +20528,79 @@
         <v>145</v>
       </c>
       <c r="D128" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E128" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F128" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G128" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H128" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="104"/>
       <c r="C129" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D129" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E129" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F129" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G129" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H129" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="104"/>
       <c r="C130" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D130" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E130" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F130" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G130" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H130" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="103" t="s">
         <v>77</v>
       </c>
@@ -20278,79 +20608,79 @@
         <v>145</v>
       </c>
       <c r="D131" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E131" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F131" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G131" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H131" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="104"/>
       <c r="C132" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D132" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E132" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F132" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G132" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H132" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="104"/>
       <c r="C133" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D133" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E133" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F133" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G133" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H133" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="103" t="s">
         <v>78</v>
       </c>
@@ -20358,79 +20688,79 @@
         <v>145</v>
       </c>
       <c r="D134" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E134" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F134" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G134" s="88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H134" s="88">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="104"/>
       <c r="C135" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D135" s="88">
-        <f t="shared" ref="D135:H144" si="17">IF(D29=1,1,D29*1.05)</f>
+        <f t="shared" ref="D135:H144" si="18">IF(D29=1,1,D29*1.05)</f>
         <v>1</v>
       </c>
       <c r="E135" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F135" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G135" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H135" s="88">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="104"/>
       <c r="C136" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D136" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E136" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F136" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G136" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H136" s="88">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B137" s="103" t="s">
         <v>79</v>
       </c>
@@ -20438,75 +20768,75 @@
         <v>145</v>
       </c>
       <c r="D137" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E137" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F137" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G137" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H137" s="88">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B138" s="104"/>
       <c r="C138" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D138" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E138" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F138" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G138" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H138" s="88">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="104"/>
       <c r="C139" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D139" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E139" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F139" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G139" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H139" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -20518,27 +20848,27 @@
         <v>147</v>
       </c>
       <c r="D140" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E140" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F140" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G140" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H140" s="88">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D141" s="86"/>
       <c r="E141" s="86"/>
       <c r="F141" s="86"/>
@@ -20556,79 +20886,79 @@
         <v>145</v>
       </c>
       <c r="D142" s="88">
-        <f t="shared" ref="D142:H151" si="18">IF(D36=1,1,D36*1.05)</f>
+        <f t="shared" ref="D142:H151" si="19">IF(D36=1,1,D36*1.05)</f>
         <v>1</v>
       </c>
       <c r="E142" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F142" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G142" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H142" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="104"/>
       <c r="C143" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D143" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E143" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F143" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G143" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H143" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="104"/>
       <c r="C144" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D144" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E144" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F144" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G144" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H144" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="103" t="s">
         <v>67</v>
       </c>
@@ -20636,79 +20966,79 @@
         <v>145</v>
       </c>
       <c r="D145" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E145" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F145" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G145" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H145" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="104"/>
       <c r="C146" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D146" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E146" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F146" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G146" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H146" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="104"/>
       <c r="C147" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D147" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E147" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F147" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G147" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H147" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="103" t="s">
         <v>77</v>
       </c>
@@ -20716,79 +21046,79 @@
         <v>145</v>
       </c>
       <c r="D148" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E148" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F148" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G148" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H148" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B149" s="104"/>
       <c r="C149" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D149" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E149" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F149" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G149" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H149" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B150" s="104"/>
       <c r="C150" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D150" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E150" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F150" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G150" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H150" s="88">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="103" t="s">
         <v>78</v>
       </c>
@@ -20796,23 +21126,23 @@
         <v>145</v>
       </c>
       <c r="D151" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E151" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F151" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G151" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H151" s="88">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -20822,23 +21152,23 @@
         <v>146</v>
       </c>
       <c r="D152" s="88">
-        <f t="shared" ref="D152:H161" si="19">IF(D46=1,1,D46*1.05)</f>
+        <f t="shared" ref="D152:H161" si="20">IF(D46=1,1,D46*1.05)</f>
         <v>1</v>
       </c>
       <c r="E152" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F152" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G152" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H152" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -20848,23 +21178,23 @@
         <v>147</v>
       </c>
       <c r="D153" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E153" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F153" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G153" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H153" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -20876,23 +21206,23 @@
         <v>145</v>
       </c>
       <c r="D154" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E154" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F154" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G154" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H154" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -20902,23 +21232,23 @@
         <v>146</v>
       </c>
       <c r="D155" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E155" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F155" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G155" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H155" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -20928,23 +21258,23 @@
         <v>147</v>
       </c>
       <c r="D156" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E156" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F156" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G156" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H156" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -20956,29 +21286,65 @@
         <v>147</v>
       </c>
       <c r="D157" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E157" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F157" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G157" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H157" s="88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="B151:B153"/>
@@ -20988,42 +21354,6 @@
     <mergeCell ref="B134:B136"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -30571,7 +30901,7 @@
         <v>183</v>
       </c>
       <c r="C12" s="90">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="90">
         <v>1.39</v>
@@ -30907,7 +31237,7 @@
         <v>300</v>
       </c>
       <c r="C35" s="90">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="D35" s="90">
         <v>1.1100000000000001</v>
@@ -31263,7 +31593,7 @@
         <v>314</v>
       </c>
       <c r="C58" s="90">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="D58" s="90">
         <v>1.74</v>
@@ -32311,10 +32641,10 @@
         <v>0.92</v>
       </c>
       <c r="D3" s="90">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="E3" s="90">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F3" s="90">
         <v>1</v>
@@ -33122,14 +33452,13 @@
         <v>0.87</v>
       </c>
       <c r="D26" s="90">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F26:O26" si="0">IF(F3=1,1,F3*0.9)</f>
         <v>1</v>
       </c>
       <c r="G26" s="90">
@@ -34051,14 +34380,13 @@
         <v>0.99</v>
       </c>
       <c r="D49" s="90">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="9">IF(E3=1,1,E3*1.05)</f>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F49:O49" si="9">IF(F3=1,1,F3*1.05)</f>
         <v>1</v>
       </c>
       <c r="G49" s="90">
@@ -35684,7 +36012,7 @@
         <v>0.10624060847171513</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>174</v>
       </c>
@@ -35710,7 +36038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>339</v>
       </c>
@@ -35730,7 +36058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>172</v>
       </c>
@@ -35756,7 +36084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>339</v>
       </c>
@@ -35776,7 +36104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>173</v>
       </c>
@@ -35802,7 +36130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>339</v>
       </c>
@@ -35822,7 +36150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>197</v>
       </c>
@@ -35848,27 +36176,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>339</v>
       </c>
       <c r="D28" s="90">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E28" s="90">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="90">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="90">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>340</v>
       </c>
@@ -35888,7 +36216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>198</v>
       </c>
@@ -35914,7 +36242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>339</v>
       </c>
@@ -35934,7 +36262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
         <v>340</v>
       </c>
@@ -35954,7 +36282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>196</v>
       </c>
@@ -35980,7 +36308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>339</v>
       </c>
@@ -36000,7 +36328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="5" t="s">
         <v>340</v>
       </c>
@@ -36020,7 +36348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>195</v>
       </c>
@@ -36046,7 +36374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
         <v>339</v>
       </c>
@@ -36066,7 +36394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="5" t="s">
         <v>340</v>
       </c>
@@ -36086,7 +36414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>194</v>
       </c>
@@ -36112,7 +36440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>339</v>
       </c>
@@ -36132,7 +36460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="5" t="s">
         <v>340</v>
       </c>
@@ -36152,7 +36480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>200</v>
       </c>
@@ -36178,7 +36506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
         <v>339</v>
       </c>
@@ -36198,7 +36526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="5" t="s">
         <v>340</v>
       </c>
@@ -36218,7 +36546,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>82</v>
       </c>
@@ -36241,7 +36569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="5" t="s">
         <v>339</v>
       </c>
@@ -36261,7 +36589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="5" t="s">
         <v>340</v>
       </c>
@@ -37107,19 +37435,19 @@
         <v>339</v>
       </c>
       <c r="D83" s="90">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E83" s="90">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F83" s="90">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G83" s="90">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H83" s="90">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -38366,19 +38694,19 @@
         <v>339</v>
       </c>
       <c r="D138" s="90">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E138" s="90">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F138" s="90">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G138" s="90">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H138" s="90">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -39306,7 +39634,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>168</v>
       </c>
@@ -39333,7 +39661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="8" t="s">
         <v>339</v>
       </c>
@@ -39350,7 +39678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>187</v>
       </c>
@@ -39377,7 +39705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="8" t="s">
         <v>339</v>
       </c>
@@ -39398,7 +39726,7 @@
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>186</v>
       </c>
@@ -39425,7 +39753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
         <v>339</v>
       </c>
@@ -40902,7 +41230,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
         <v>67</v>
       </c>
@@ -40915,7 +41243,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
         <v>77</v>
       </c>

--- a/inputs/en/LiST countries/SYR_databook.xlsx
+++ b/inputs/en/LiST countries/SYR_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Testing June 2025\Databooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tharindu Documents\WB_multi_country 2025_R1\Databooks_R1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6E7560F-4AB3-41E3-87CD-4906497FA7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F49B01F-5E14-472B-97FB-599EBB68AF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="961" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -2690,6 +2690,74 @@
         </r>
       </text>
     </comment>
+    <comment ref="L37" authorId="1" shapeId="0" xr:uid="{B53E2CCE-449F-4B13-937B-3F8B887F6752}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="1" shapeId="0" xr:uid="{1148A5A1-251A-4064-B40F-0C8735779040}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="1" shapeId="0" xr:uid="{15C867EE-F338-4C14-9C7D-F0E3CF1EF5FB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O37" authorId="1" shapeId="0" xr:uid="{8E4E4ECE-5F5C-4FD8-8945-6257CBFF139B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
@@ -3928,7 +3996,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{6BB5D3EA-EB2C-4557-A77A-BC3B31DE5A74}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{E6EBA730-3C9A-42F5-8372-C12E3D2BCF23}">
       <text>
         <r>
           <rPr>
@@ -3942,7 +4010,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{8276B184-5391-46AC-9017-CD45ED68E7E2}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{AF9DB01E-B712-4A66-A517-1C057B372D40}">
       <text>
         <r>
           <rPr>
@@ -3956,7 +4024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{70662288-9B2B-4D49-A059-B389A408D887}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{207C9149-2C56-40E5-890F-83153B938A2F}">
       <text>
         <r>
           <rPr>
@@ -3970,7 +4038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{5F99FF59-4E44-4847-82EE-D42B7418AA00}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{39C4CB92-7EE0-4046-B67E-41191387FFA0}">
       <text>
         <r>
           <rPr>
@@ -3984,7 +4052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{F6C9465E-FBDE-45D1-8394-CD6F9C9C2529}">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{E377B1E7-A333-4A74-97C3-029328512C07}">
       <text>
         <r>
           <rPr>
@@ -3998,7 +4066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{8724D448-9507-4D14-BCA7-F21B3CAF1BD6}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{200C4BAB-9EE2-447E-A6DD-80717CFE4AC8}">
       <text>
         <r>
           <rPr>
@@ -4012,7 +4080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{1D086CE7-3639-4C5A-8FD3-DB935503731C}">
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{9FC7E5D2-2D8B-4961-9B75-5691D4A68B0C}">
       <text>
         <r>
           <rPr>
@@ -4026,7 +4094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{1EDBAC82-3035-4B47-8DB4-6C9605D373FF}">
+    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{D951D76C-28E5-48CE-899C-D128152950FC}">
       <text>
         <r>
           <rPr>
@@ -4040,7 +4108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{F889FFDD-F5D3-428F-97C9-3FA317F4DEEC}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{E9DCEC9B-12F6-42CF-8CD9-B1C5DD42DE71}">
       <text>
         <r>
           <rPr>
@@ -4054,7 +4122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{178C61B9-10CF-475E-AE2A-1148BD159501}">
+    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{9FD33C3F-D78F-4E9D-A67C-9D39AC73491A}">
       <text>
         <r>
           <rPr>
@@ -4068,7 +4136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{D1ADD6AA-00B3-496F-889D-6AD9E8EC7261}">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{3400288E-DF03-41FF-B1F2-3EB20AA1B927}">
       <text>
         <r>
           <rPr>
@@ -4082,7 +4150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{D8A7821F-2C8B-4B9F-B2CF-783B6F1D6ACB}">
+    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{9C325214-076C-49F4-9A1C-FDD39C7EF1F6}">
       <text>
         <r>
           <rPr>
@@ -4096,7 +4164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{30A88894-D578-48EA-8642-A1FBFF69A3C1}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{9B6733C4-FA93-4154-8674-5B85D19B6115}">
       <text>
         <r>
           <rPr>
@@ -4110,7 +4178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{1FC0B5F8-9FC2-4095-AEC3-321F62EB13E4}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{0607EB3C-B9C7-4D01-AE82-3B20B34591B6}">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{037243D6-BCDE-4F6B-AFCC-3F94A0DD5E02}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{26DD0551-BD1F-450A-8953-951E786BA725}">
       <text>
         <r>
           <rPr>
@@ -4138,7 +4206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{DE335ADC-5DD3-496C-A5AC-AAE47036457E}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{07B0F43C-E3A4-41A5-9220-14111D4DE5D5}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{2912EBE3-D556-42B6-96D5-24EC21E6156C}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{BF774CA2-E4B3-46E6-A04D-901C8156EE77}">
       <text>
         <r>
           <rPr>
@@ -4166,7 +4234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{4CB9182B-79CD-4596-8295-56AF4E3846AB}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{DDFF231A-B050-4E30-B877-4FB8473D71B0}">
       <text>
         <r>
           <rPr>
@@ -4180,7 +4248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{80F6289A-949B-4FAE-AC85-22980BCEA4F4}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{0214BC76-CC8A-414C-8D7A-C51B3E742D6B}">
       <text>
         <r>
           <rPr>
@@ -4204,7 +4272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{96FCBC9B-E5EC-46B8-8DF3-3E8D35EE350D}">
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{408E5496-8B3D-4F1E-BD84-9A9255C25832}">
       <text>
         <r>
           <rPr>
@@ -4218,7 +4286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{93171B53-CE10-41E2-9E96-E27147D4D778}">
+    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{DF0EEE5A-AAEC-4832-9B3D-B069B0FD3D24}">
       <text>
         <r>
           <rPr>
@@ -4232,7 +4300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{5FE03E37-E69F-43F4-B94E-7BBC3063A87D}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{2A9C86D6-9952-4010-8EF5-ED482E1554FE}">
       <text>
         <r>
           <rPr>
@@ -4247,7 +4315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{626B60BA-B78A-4BE5-ACC0-D15C014DDDE7}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{5A70274A-2FB2-4238-A065-120459AD1B15}">
       <text>
         <r>
           <rPr>
@@ -4262,7 +4330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{A6D7FDB2-70C1-4A3F-AE05-E1F583DAC911}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{385F9BE4-A3AC-4198-BAC3-722E7A520402}">
       <text>
         <r>
           <rPr>
@@ -4277,7 +4345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{73FE6ADA-DBBD-4E18-9E0A-7E9F1B65F4FF}">
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{1E0B57C8-7A0A-48E3-A3E8-1E19A7175498}">
       <text>
         <r>
           <rPr>
@@ -4292,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{36DC02C6-7D52-483D-9E4D-A62E1832D1E9}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{2AC9637A-4534-4154-9BD7-3AE7DD8CD9DD}">
       <text>
         <r>
           <rPr>
@@ -4307,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{3A418ECB-CB98-4DAE-914F-181BDF7ED565}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{01A3CEF9-0D30-4FDB-AF26-2DC31C7D29F6}">
       <text>
         <r>
           <rPr>
@@ -4322,7 +4390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{F54E6507-D7CB-4F8D-8BA0-8C678AC88484}">
+    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{E3448607-813B-4893-BFAF-1777B6724FBF}">
       <text>
         <r>
           <rPr>
@@ -4337,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{51D136EC-624C-44D3-B5B3-53EE7A4C79F4}">
+    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{CB33591A-EF28-41CE-A9F1-ECF332B1A04F}">
       <text>
         <r>
           <rPr>
@@ -4352,7 +4420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{0358037B-23C7-469B-B136-BD3C312D371A}">
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{652EDCEE-9F4F-4011-BE3F-87A81AEAB68F}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{83DD7CE2-EBA6-4C72-A5A2-1E7961104F35}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{F2E7DF39-BD3C-4774-9BD5-66837E9E22BF}">
       <text>
         <r>
           <rPr>
@@ -4380,7 +4448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{D00C0728-6CE5-4232-9E9D-03298AA7E83F}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{84346A43-22E1-4209-86B7-5484553C9A3C}">
       <text>
         <r>
           <rPr>
@@ -4394,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{DE005C0A-2F8A-418C-851E-64B2B8CFE1FA}">
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{6AA73D8B-E906-4C63-9A89-433F265EDADB}">
       <text>
         <r>
           <rPr>
@@ -4408,7 +4476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{E55324F7-370C-4385-ADBA-E8B0EBEB4BEC}">
+    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{D0DB495D-46B4-4957-B9C2-D1B5214046C5}">
       <text>
         <r>
           <rPr>
@@ -4422,7 +4490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{F53439F8-F18B-45A1-B265-14A4B9BFCA4E}">
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{E8F934AE-F36A-4978-A2B4-5231B12CD33F}">
       <text>
         <r>
           <rPr>
@@ -4436,7 +4504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{D3552897-BBD5-4175-B68A-A3F1E4A6E75C}">
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{53D9CECE-9FA0-4330-B76A-C6EEC6C1D659}">
       <text>
         <r>
           <rPr>
@@ -4450,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{CC47941B-D047-44AD-8609-225A3A1207CF}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{9DC905D6-8DE5-4FE7-BE6F-D3E934A75201}">
       <text>
         <r>
           <rPr>
@@ -4464,7 +4532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{0CBE3706-3924-4509-A583-88069D4C218C}">
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{ACC4B3F7-E558-402F-BE57-0C3DDC8060F5}">
       <text>
         <r>
           <rPr>
@@ -4478,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{A5F6F3D3-D70F-4D04-A795-6D6BF5E34983}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{955FA18E-86F7-422C-8CA5-A38FE4881347}">
       <text>
         <r>
           <rPr>
@@ -4492,7 +4560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{DD598447-A738-4E83-BE84-12132D14A7E3}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{33441C3A-E101-49E5-A4DB-504F222DBABB}">
       <text>
         <r>
           <rPr>
@@ -4507,7 +4575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{AAC1265A-FBA5-4B61-B6FD-C1ADAB02C015}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{9A6BDF27-568B-45B9-BE8D-362C80D286A5}">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{CB5BEA38-52BE-4279-8999-876D134092DA}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{08FA6FC1-5E34-45F1-9F8B-4E7BAEF15D4E}">
       <text>
         <r>
           <rPr>
@@ -4537,7 +4605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{EEC82E46-7238-472F-8156-89C286EC0CC5}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{E9730E75-4547-4DE1-A9F2-FCA6D5B09778}">
       <text>
         <r>
           <rPr>
@@ -4552,7 +4620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{9AD99541-38BF-452C-BBDF-30A63672B134}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{38945CFE-2923-4A7C-9E0E-820E103F12F0}">
       <text>
         <r>
           <rPr>
@@ -4567,7 +4635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{9F2485E2-4FB1-40DF-95BC-EF307614F383}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{F76610CF-AE5A-4A2B-BD5A-C60057991BBE}">
       <text>
         <r>
           <rPr>
@@ -4583,7 +4651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{5A344499-6486-4E45-BC00-E472735A7CB2}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{8EC67AD9-5004-458A-B78A-27343190877D}">
       <text>
         <r>
           <rPr>
@@ -4599,7 +4667,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{031BB5AD-8138-4687-BD78-7EBC20A98663}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{8D6C5816-8BDB-4D07-A205-24F2394A4590}">
       <text>
         <r>
           <rPr>
@@ -4615,7 +4683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{184A5B5A-1F15-44FE-898C-B90309E01D89}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{B76A1BFB-64B6-4C17-9732-138D8EB49340}">
       <text>
         <r>
           <rPr>
@@ -4631,7 +4699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{8ED585B4-389F-460E-8916-C9CBE4D87E3D}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{962C7931-87AA-452E-BF56-06BF5EBED30C}">
       <text>
         <r>
           <rPr>
@@ -4647,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{AD24A257-1231-432A-9AC2-49A1BBCFE8E5}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{25F108DC-6C32-4B96-9492-1B12A3709CE9}">
       <text>
         <r>
           <rPr>
@@ -4662,7 +4730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{A07ED250-D084-453F-8461-66EC0C10E110}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{8B1376CD-B39F-49F6-BC5B-7A2858E0592C}">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{9059BCA8-1FD3-4E64-86A7-3061E1F307E3}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{048CF327-553B-4B14-8A84-22CC73D47D4A}">
       <text>
         <r>
           <rPr>
@@ -4692,7 +4760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{7052734F-4036-424E-8991-EAD18C6FC7CF}">
+    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{1FFD936D-DA45-475C-9F30-391304B2787A}">
       <text>
         <r>
           <rPr>
@@ -4707,7 +4775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{9211745A-0C8C-4E89-B62F-2D6F1D5B7D01}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{3CED59C7-FFD8-4D8E-9210-1FB3B9F57245}">
       <text>
         <r>
           <rPr>
@@ -4722,7 +4790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{5423B35A-FBAB-43E1-A574-44F7790EAEA1}">
+    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{BFC97A30-BB96-4307-90EA-5BE03611C63A}">
       <text>
         <r>
           <rPr>
@@ -4736,7 +4804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{9923839E-0345-401E-8DBE-0D84F514E4A9}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{51ED88B2-1E5E-47FC-9698-0E5AB645D504}">
       <text>
         <r>
           <rPr>
@@ -4750,7 +4818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{BA7FE3E3-08B4-4F16-B01F-05A523005C56}">
+    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{561CB528-6BAE-4817-8CC0-243735B76FA1}">
       <text>
         <r>
           <rPr>
@@ -4764,7 +4832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{6D26BBC2-8403-47E0-89A8-CCA5B5E2A63F}">
+    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{E496632C-74C0-41C8-9AB4-0B4C87893674}">
       <text>
         <r>
           <rPr>
@@ -4778,7 +4846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{4063B8B9-975B-4060-938A-48F03FAEF419}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{FBF69FC4-CD17-4513-AF48-E695A29BF824}">
       <text>
         <r>
           <rPr>
@@ -4792,7 +4860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{50660BAB-9FCC-42B5-9F93-0DBB8CA89897}">
+    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{900E651E-9020-4856-BB60-BF507FACE1CC}">
       <text>
         <r>
           <rPr>
@@ -4806,7 +4874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{C6A07F78-8D75-479F-926E-474BA841B234}">
+    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{49F9B2F7-6FD6-4FDF-921C-425B5CDD5155}">
       <text>
         <r>
           <rPr>
@@ -4820,7 +4888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{FA86AF70-4991-447A-BCAA-1000A44BF256}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{4AC52846-7242-459E-9C8D-BF78F201C110}">
       <text>
         <r>
           <rPr>
@@ -4834,7 +4902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{FD47D524-CA3E-4654-B95C-882313C71EE4}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{B7E52F08-0E63-474C-A17D-FB71B12C1A4F}">
       <text>
         <r>
           <rPr>
@@ -4848,7 +4916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{350D10EC-94B3-4790-8891-B0A27313C3E5}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{329CDC5B-FBD8-45AA-9D30-2F9915F0B0DB}">
       <text>
         <r>
           <rPr>
@@ -4862,7 +4930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{E54F70F0-DBA3-4F25-90EB-D1DFD3641E6A}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{74D24310-E8B6-4724-B08F-C246A0B86F17}">
       <text>
         <r>
           <rPr>
@@ -4876,7 +4944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{77363AFB-2A43-477F-8EB8-CC2F7E3ECEA0}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{7026E01B-E53C-4032-904B-4C8C6143328A}">
       <text>
         <r>
           <rPr>
@@ -4890,7 +4958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{01109C22-04ED-4FDB-949C-C34810AB2E95}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{56E6B52D-1C74-48A6-AB95-D033A5B5881A}">
       <text>
         <r>
           <rPr>
@@ -4904,7 +4972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{72F3E256-254B-4FFC-9E01-1752BCF475A6}">
+    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{A2996F6D-43C2-499B-8B4D-F7E668692366}">
       <text>
         <r>
           <rPr>
@@ -4918,7 +4986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{E057EF81-59F3-42CB-9D3F-907D93019067}">
+    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{1BA30CAA-FFAB-42ED-B857-7C2DBF6DD53A}">
       <text>
         <r>
           <rPr>
@@ -4932,7 +5000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{DF457454-4973-4207-9E3D-7D50D7830FDE}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{234E5DD0-50F5-435F-A2AD-FDCE2659B300}">
       <text>
         <r>
           <rPr>
@@ -4946,7 +5014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{0A31E4B1-743B-4208-AE2B-4146BBD81A93}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{81B268C8-266C-41E0-8968-7FD59EF44415}">
       <text>
         <r>
           <rPr>
@@ -4960,7 +5028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{BA5122FC-4C8D-49F0-9902-8C88B2457CA4}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{D68CDFE1-6866-4AC0-B4D7-B34E1A995637}">
       <text>
         <r>
           <rPr>
@@ -4974,7 +5042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{EB775666-1A82-4D30-A432-4C033A1A7AED}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{6447B983-C337-44DD-BE06-3BF10916980C}">
       <text>
         <r>
           <rPr>
@@ -4988,7 +5056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{98BB8C6D-B30B-4DB6-8B35-7D8DCE93E79C}">
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{42AC3582-1D7E-471B-A6C7-CD7E77F8588B}">
       <text>
         <r>
           <rPr>
@@ -5003,7 +5071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{75544419-0995-4A7F-98E3-CBE19D6471D0}">
+    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{C499C901-0DF0-4641-8493-EE778DE73B96}">
       <text>
         <r>
           <rPr>
@@ -5018,7 +5086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{866B3636-D1B7-40EE-A9B3-22FD1891C340}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{080FF01F-34D3-44B7-835E-C7CC7A5B457C}">
       <text>
         <r>
           <rPr>
@@ -5033,7 +5101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{3C5743BD-EFCC-4AF2-B330-6FDF8775A9D5}">
+    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{B263C3DB-9806-4F53-B7FE-F5AB30086A04}">
       <text>
         <r>
           <rPr>
@@ -5048,7 +5116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{07C4191C-0E34-4B64-AAF8-A7F551741AB2}">
+    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{FF88E7CE-1D54-4693-9AC1-0680C2879226}">
       <text>
         <r>
           <rPr>
@@ -5063,7 +5131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{419B2D75-98C1-46B5-842D-118FC911FF04}">
+    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{F32BE7CD-2AAA-47AD-914F-4CAAC1FEDD3B}">
       <text>
         <r>
           <rPr>
@@ -5078,7 +5146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{A1CD6A7F-EF69-49BD-84EA-F060EB24114F}">
+    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{BCFCAE2C-B071-4EBD-916E-9CB34A3AE95A}">
       <text>
         <r>
           <rPr>
@@ -5093,7 +5161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{D5825461-688C-438C-8542-BD85D579FDC7}">
+    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{E2890E16-5EE9-49DE-B974-B3ADDC0025FE}">
       <text>
         <r>
           <rPr>
@@ -5108,7 +5176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{AF7C92B2-AC28-43C3-9C19-D68E37FF28FD}">
+    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{FFC68E24-6D1B-4208-B66E-D8A12166F7EF}">
       <text>
         <r>
           <rPr>
@@ -5123,7 +5191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{700142E9-6A7D-415A-8AA2-F2A8B6A75555}">
+    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{AE98D75E-0886-4415-A5FC-355EDA6C4FF5}">
       <text>
         <r>
           <rPr>
@@ -5138,7 +5206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{7D67AB3C-983B-47D0-9AFF-DA097636CBA4}">
+    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{F3FF4EFF-507E-406A-9019-C50AD187D27F}">
       <text>
         <r>
           <rPr>
@@ -5152,7 +5220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{38FC6B21-5384-4027-AE29-F2FF12011A26}">
+    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{DE5B9A2C-A2CF-41B4-A227-60CE716BCCA3}">
       <text>
         <r>
           <rPr>
@@ -5166,7 +5234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{EB3D123B-E86C-4173-B872-21E041277078}">
+    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{34EEDC69-740F-43FD-A983-6FB9711FB123}">
       <text>
         <r>
           <rPr>
@@ -5180,7 +5248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C5BAFDF7-3C0B-454A-B8DD-17A5272728F7}">
+    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C1C7CF2A-6820-4496-B5B3-46A027800BF9}">
       <text>
         <r>
           <rPr>
@@ -5194,7 +5262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{BB84B4E6-6EBF-43F8-A27F-ABACD68A728A}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{EBC10A23-30BF-4E42-8CA2-8EE10D6CA31A}">
       <text>
         <r>
           <rPr>
@@ -5208,7 +5276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{BFD18A89-7D4A-4FA5-8D9C-46BDFC49F7B4}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{C4570B06-D8B9-4BF0-8899-481D28F107D4}">
       <text>
         <r>
           <rPr>
@@ -5223,7 +5291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{1ABF9016-F3C2-48B1-BD46-AD89F4003AC8}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{E10AAA50-CCAF-4DFB-8CEA-438EA6695142}">
       <text>
         <r>
           <rPr>
@@ -5238,7 +5306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{6A6E8E29-2989-40FF-B168-55803883F0D8}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{0D2DBAA3-0B85-4069-9696-DDECC83557DF}">
       <text>
         <r>
           <rPr>
@@ -5253,7 +5321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{48DA76B4-3665-4A45-819A-BFEEFF70E5D8}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{E6F4F3F2-6816-43AD-9558-8D77B03CE641}">
       <text>
         <r>
           <rPr>
@@ -5268,7 +5336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{B80ED8C6-87BC-498B-8629-005BCCE79F4B}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{994813E0-DC6E-4867-8FA2-13765D152F5E}">
       <text>
         <r>
           <rPr>
@@ -5283,7 +5351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{B5F2ED77-4534-4005-9653-3943813A8B21}">
+    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{6D709644-E2DA-4998-B8D6-CCE8241FA062}">
       <text>
         <r>
           <rPr>
@@ -5299,7 +5367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{76285A74-606B-4904-9089-8C072E19A125}">
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{E0BF8484-6C50-4B90-B5C7-81D81EF18053}">
       <text>
         <r>
           <rPr>
@@ -5315,7 +5383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{63134AD8-900C-4178-BB9D-773F5A2AEB3B}">
+    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{98B23DB2-DC71-4976-B9E0-A2E971751C45}">
       <text>
         <r>
           <rPr>
@@ -5331,7 +5399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{E4550204-DAD5-4F24-9613-4B653BB1BEF9}">
+    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{EED7AE56-914C-4919-99D9-9B4DD94D01A5}">
       <text>
         <r>
           <rPr>
@@ -5347,7 +5415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{8EB04C99-52A7-4C56-9738-8833ED4CF79E}">
+    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{C946989D-0B8C-452F-9FD8-02724BD02182}">
       <text>
         <r>
           <rPr>
@@ -5363,7 +5431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{1E087D6A-9C87-4366-B106-9662D0E9F522}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{E509D43A-5096-49C2-BA18-0C199C6BF4A8}">
       <text>
         <r>
           <rPr>
@@ -5378,7 +5446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{9524A10F-3B35-4B50-9361-07DEAF9EC66F}">
+    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{7D8578B9-425B-43DC-B215-7EF10F08E80C}">
       <text>
         <r>
           <rPr>
@@ -5393,7 +5461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00995C78-B5BF-45A5-8F02-B4D6CB8053C5}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{309E82E0-67AD-454E-9A05-4D9313B66A93}">
       <text>
         <r>
           <rPr>
@@ -5408,7 +5476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B614B807-4445-457C-8B76-0D078F087764}">
+    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B9EF8017-E5A0-4B1E-9AF7-1E695ECA49AB}">
       <text>
         <r>
           <rPr>
@@ -5423,7 +5491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{4A9ECB14-4CB2-41BF-A402-F7A28029EC10}">
+    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{26E77479-1563-4266-B2C1-17AF174C9575}">
       <text>
         <r>
           <rPr>
@@ -5438,7 +5506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{B642BE55-802D-4C94-B750-1AEA253BACA7}">
+    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{09D666FE-E28F-48AE-ADF8-2D96C595DB94}">
       <text>
         <r>
           <rPr>
@@ -5452,7 +5520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{CE9B9D72-3B1C-4412-9D79-6D0874D60CEE}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{B9267817-21CE-42E6-A675-E3EF4A926E99}">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{AB5427B8-7880-46F7-8737-0E11C545B3E1}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{D5F41D35-9589-4734-9273-1246C82D90D3}">
       <text>
         <r>
           <rPr>
@@ -5480,7 +5548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{7DADC3D7-B312-4F80-917D-FD030194B70F}">
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{68C36586-6425-44D5-AE71-7B83AC0B0D80}">
       <text>
         <r>
           <rPr>
@@ -5494,7 +5562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{E932DAA3-B84B-48A0-A350-BB68775D7800}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{EAF8C373-AE13-4606-898A-ED625C16452F}">
       <text>
         <r>
           <rPr>
@@ -5508,7 +5576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{75AFBBA3-C0BF-47C9-96C1-E2BCE0A5518C}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{A99AB4B1-F894-4133-B7CD-69537AC87FC8}">
       <text>
         <r>
           <rPr>
@@ -5522,7 +5590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{44B4DAC8-1128-45E5-B99C-C84974BBEE0A}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{66812343-2E7C-44E8-B27C-8CF88CE05138}">
       <text>
         <r>
           <rPr>
@@ -5536,7 +5604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{BFC250B8-BAEB-445C-954D-7BE97AABDFDB}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{384DF3D1-4AA8-4943-A530-5AAE715E42E7}">
       <text>
         <r>
           <rPr>
@@ -5550,7 +5618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{AEC7DAF2-9B1C-4CBB-B735-E9AB7A0CFD03}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{1DE26347-7149-43FD-858E-465A040CC0F3}">
       <text>
         <r>
           <rPr>
@@ -5564,7 +5632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{5757C298-3224-4FCB-AE44-57AE2804657A}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B687D13E-D130-42E7-9D6A-3F80F0C7EF5D}">
       <text>
         <r>
           <rPr>
@@ -5578,7 +5646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{32018E11-B6CC-4CB9-AD83-CDEAB15CB02F}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{9BC31D67-F810-46D7-B5A1-4288AAC1F5B6}">
       <text>
         <r>
           <rPr>
@@ -5592,7 +5660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{548CA939-8049-4A22-8DCF-97B43275D455}">
+    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{64D245B3-8DA5-40BE-BC14-2456737D9F8E}">
       <text>
         <r>
           <rPr>
@@ -5606,7 +5674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{B79D2BBE-1689-4CA2-9F3C-27F21A096995}">
+    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{5798986F-DE4D-469D-8D38-C4A254954155}">
       <text>
         <r>
           <rPr>
@@ -5620,7 +5688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{521B8842-9FA3-4AE6-9999-7E38BD5734E2}">
+    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{1683DE01-9F25-40E0-AE29-344104540630}">
       <text>
         <r>
           <rPr>
@@ -5634,7 +5702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{745C521C-CEC3-4590-B658-F244E03502B3}">
+    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{6E399964-9FF6-4F4D-B47E-AC805C54B9BA}">
       <text>
         <r>
           <rPr>
@@ -5648,7 +5716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{48501DF5-33AD-4137-BF61-A1ACEF3712BB}">
+    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{EFF89D0F-5E10-4447-B0BA-64F660AD6D14}">
       <text>
         <r>
           <rPr>
@@ -5662,7 +5730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{52DA180B-0E50-41F0-B433-76D057FD32AA}">
+    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{E024415B-2F81-4A00-9886-75203AC76837}">
       <text>
         <r>
           <rPr>
@@ -5676,7 +5744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{1827DF80-3E7F-4FAE-B545-321A48A20B7F}">
+    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{773BC8B9-C7FD-4E1D-BFAD-28167A2B0241}">
       <text>
         <r>
           <rPr>
@@ -5690,7 +5758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{428ADF28-94CB-45A6-B512-653753D79D4A}">
+    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{E0893EE6-8215-43BF-B8DC-C2BA125EF501}">
       <text>
         <r>
           <rPr>
@@ -5704,7 +5772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{E327363C-87BF-426D-8031-8E5B15B868F6}">
+    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{B0106407-B25E-404E-AE98-C6E846DE7439}">
       <text>
         <r>
           <rPr>
@@ -5719,7 +5787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{0FC0F10D-E16C-4929-8C9C-BBCE7D585B2C}">
+    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{B3781CC1-6735-4678-95E3-B6650A0CF979}">
       <text>
         <r>
           <rPr>
@@ -5734,7 +5802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{83AA2241-D1A0-473B-BB01-4502DE008F6C}">
+    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{550CF970-1632-472E-99A6-5157A6C70FB5}">
       <text>
         <r>
           <rPr>
@@ -5749,7 +5817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{AB840D19-E9DC-41E5-8B1A-28772D27BB6F}">
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{0F529DF4-B0D9-4A77-880D-52378457049B}">
       <text>
         <r>
           <rPr>
@@ -5764,7 +5832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{28DA7237-5B4A-4888-B612-1517D8E4181A}">
+    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{0A749486-D0DA-44DD-A158-4937B013D9E1}">
       <text>
         <r>
           <rPr>
@@ -5779,7 +5847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{24B15358-0318-4650-A1D9-ACBF45D6BD86}">
+    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{65A87F96-9920-4AFF-9D42-432A9BC46A37}">
       <text>
         <r>
           <rPr>
@@ -5794,7 +5862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{3CCBD856-2028-4562-873C-EF798B7CEB0E}">
+    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{14AFEBEB-6E6D-485B-AD84-D77832449F6B}">
       <text>
         <r>
           <rPr>
@@ -5809,7 +5877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{515C103F-DDC3-40D5-AA24-3704C957FBDF}">
+    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{C956521D-520C-46E0-BBF9-22BA4AB5823B}">
       <text>
         <r>
           <rPr>
@@ -5824,7 +5892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{2B07245A-D9DE-402F-8C94-59F9204780AD}">
+    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{889435D0-F1CE-49D5-B3FA-2C346C3DD8BB}">
       <text>
         <r>
           <rPr>
@@ -5839,7 +5907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{B09F6ACE-9930-4B23-AC49-D976E3AF6D20}">
+    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{21DCB560-D7D0-454D-9256-2EB6BA5D9FAF}">
       <text>
         <r>
           <rPr>
@@ -5854,7 +5922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{08D07A70-B0BF-4318-BF4F-F0DBC6170F84}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{2CA48B3A-F458-496E-A12E-9EDFF9710F14}">
       <text>
         <r>
           <rPr>
@@ -5868,7 +5936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{76EC0005-9898-4CC7-A802-EC15F25448F0}">
+    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{D5130B5B-6564-4541-AFF7-B31DC2A99F0C}">
       <text>
         <r>
           <rPr>
@@ -5882,7 +5950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{E5FFA232-5153-4095-946B-DFA45A9FBF8C}">
+    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{A87CEC0D-D5EC-411A-9E0A-45792CF26B1E}">
       <text>
         <r>
           <rPr>
@@ -5896,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{AFCCFA07-E0EB-45D3-B7C0-514815792647}">
+    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{F07A7990-2D7C-41E0-8069-25EED27A8B7D}">
       <text>
         <r>
           <rPr>
@@ -5910,7 +5978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{C392BCAD-8C69-4A4C-87EF-377772EECC28}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{B9A5DC53-F533-4CB3-94F1-5C0DF398AC61}">
       <text>
         <r>
           <rPr>
@@ -5924,7 +5992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{E3317A10-0BE4-48FF-9352-A01B5BA3FEE5}">
+    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{F61BC170-6314-4BE8-BD27-ACBE21EC6D83}">
       <text>
         <r>
           <rPr>
@@ -5939,7 +6007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{67EC6033-7BEB-4400-84EE-0A8533A907FD}">
+    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{F2F9EF38-F3FC-4F8C-BAEA-4602406D7D4B}">
       <text>
         <r>
           <rPr>
@@ -5954,7 +6022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{E94FC89C-5249-427A-BE28-D6BFC2F81758}">
+    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{03156B19-EF6A-4B80-952F-EA4B39906AB2}">
       <text>
         <r>
           <rPr>
@@ -5969,7 +6037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{AA56A34D-E716-48F4-B898-FA37D2EF7D4D}">
+    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{6C70B7FC-07DB-4AA6-AD5D-BA8D185F69A2}">
       <text>
         <r>
           <rPr>
@@ -5984,7 +6052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{90492BA0-E368-47BA-98D1-DF7E39D86EF5}">
+    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{ECCF229F-BC05-441A-A8EC-996A647C989C}">
       <text>
         <r>
           <rPr>
@@ -5999,7 +6067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{9CD81021-C7F5-4F80-9E36-5A372FBC35BF}">
+    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{853363A1-995D-434E-99B9-CBFFCC587E17}">
       <text>
         <r>
           <rPr>
@@ -6015,7 +6083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{49DF1121-32A1-4036-AEE8-BCAAA6147B06}">
+    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{D7049EC9-BADF-40DE-979A-0A74E0293BB1}">
       <text>
         <r>
           <rPr>
@@ -6031,7 +6099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{9499DF21-B57E-420A-A749-CC9BF2D4D725}">
+    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{C916B5A2-27DC-436D-B575-9210A24C214D}">
       <text>
         <r>
           <rPr>
@@ -6047,7 +6115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{4524A951-07DC-487B-A233-43D4EAAEC701}">
+    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{D9F9FF7F-8008-4D79-ABB3-028FF22CD559}">
       <text>
         <r>
           <rPr>
@@ -6063,7 +6131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{889D9E25-29F0-4C18-931F-58D4600ECBE1}">
+    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{D7D5CD6A-B8A4-4771-AAA0-5113E0A3BC1F}">
       <text>
         <r>
           <rPr>
@@ -6079,7 +6147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{678FE956-BF94-4DA4-81E3-20DDE72682D7}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{06B708C5-CF4C-4BD9-A112-999F5C581700}">
       <text>
         <r>
           <rPr>
@@ -6094,7 +6162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{6CE9DBC0-F411-450C-ADE5-6FE43AB51348}">
+    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{652C7700-A4E9-41DE-B7A6-091614D48006}">
       <text>
         <r>
           <rPr>
@@ -6109,7 +6177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{F2C8AB55-E76F-4187-99C2-69AB2BD9809A}">
+    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{C648195E-E2CA-46F6-BED8-ABE76E4EB10D}">
       <text>
         <r>
           <rPr>
@@ -6124,7 +6192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{D025E63E-9D67-4225-8627-D53B10AA6DB9}">
+    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{876F0647-9D39-464F-9AEF-66CCB9E7BEE5}">
       <text>
         <r>
           <rPr>
@@ -6139,7 +6207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{E220EC8B-3A48-4133-BD12-15E3EB9F00B6}">
+    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{A2FD75B6-2FF3-4112-A257-87C89428A222}">
       <text>
         <r>
           <rPr>
@@ -6154,7 +6222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{74D29CD4-44A4-4706-B0D2-5EBDC4B70B6C}">
+    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{17B0E3BD-602F-47AD-8FDA-505C553A7C4F}">
       <text>
         <r>
           <rPr>
@@ -20853,6 +20921,35 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B142:B144"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B111:B113"/>
@@ -20869,35 +20966,6 @@
     <mergeCell ref="B98:B100"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -33584,16 +33652,16 @@
         <v>1</v>
       </c>
       <c r="L33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="M33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="N33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="O33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -33791,16 +33859,20 @@
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <v>1</v>
+        <f>L31</f>
+        <v>0.38</v>
       </c>
       <c r="M37" s="90">
-        <v>1</v>
+        <f>M31</f>
+        <v>0.38</v>
       </c>
       <c r="N37" s="90">
-        <v>1</v>
+        <f>N31</f>
+        <v>0.38</v>
       </c>
       <c r="O37" s="90">
-        <v>1</v>
+        <f>O31</f>
+        <v>0.38</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -34722,16 +34794,20 @@
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <v>1</v>
+        <f>L54</f>
+        <v>0.7</v>
       </c>
       <c r="M60" s="90">
-        <v>1</v>
+        <f t="shared" ref="M60:O60" si="16">M54</f>
+        <v>0.7</v>
       </c>
       <c r="N60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
       <c r="O60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34753,39 +34829,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="16">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="17">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34800,11 +34876,11 @@
         <v>165</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:D67" si="17">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="18">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
@@ -34846,11 +34922,11 @@
         <v>166</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
@@ -34892,11 +34968,11 @@
         <v>167</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
@@ -34938,11 +35014,11 @@
         <v>175</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
@@ -34980,7 +35056,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TBm5n0F3ZSMKrCjY+AL4slUg0hXT2hO+5shU+GoRiFXJBcHFkYgPBlqs+Fxx6PFsQewttQOR21aj1fXZcoz8ag==" saltValue="SognIhr+7Tvq4ZYvkkpSZA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="O9b9DvQJo3G6KJNUNq8X2QehGOtFR5U6yKm/syA6NM1J0lvXdCmzZlnKyhbrPClx1ZNPC01gUAZ+jhIfjrbLLQ==" saltValue="1U2JdgVE5zlYBKfyTDTw3A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35262,7 +35338,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1Mri6mDNakxTN++LYDkrSlnJ4hCf3+16Ur3JzKHbXsgMLeiOx4246djFaBfqw7/DRWYE8TBQn+gwoEULaV5KRw==" saltValue="hCtPYkilVxJaj3uZrBsg0A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LnHqzSn11/I1WCwvgSV/aFkE4DJCKbxU6E+/fckfwuo9TSYYFU2r03FX6SuodzE0Icw7QU7yQRDXQkg8mnkbQw==" saltValue="YhMnDcTLXSaovyjlmfHDMw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -39122,7 +39198,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QZuJBLT18RLClOQpds4MuooJcG/7vFHLggKJjPvPOQAFJAkJ01ilC4kkb2DTiT5pCXWheznDmX2e8pP9U30oZA==" saltValue="StP3eyhH6xyKX3Qyhj6KZw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sHld8DXHNvBPvgOxgonJEdNr45oJ9dhGm4EyeRR/kJgZwuRtQOqpKRwAGWgbK7p0KPrU1sXLs5MI5cYHa/DMFQ==" saltValue="ExAPAhIxQbwU8rsTTgoi4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39762,7 +39838,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rBj4/xhupbkAjC3P8LLaOOabRcINjXHoySh1ckSTSXgOjYOIfIAjJmLR21rEgF+VA5vPMQjl2MeTTNpp+BUspw==" saltValue="QX9aSRqCF7tm0vhyOJqcEw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+Rt7ZWqFE4X26qXz/KjecTkQKgctzAjXiAuwem7Q53yDZR2yMdoSjy31bFNSh3+37+vm43wZuMN9UQUzoZI9/g==" saltValue="DN4zRpZshXPaqZQnWOz1eg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41805,8 +41881,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57ec1f31440e439775915f75cb7954ca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="62245b0892ab2a20b5f44f74e1fbf663" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -41988,15 +42073,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
   <ds:schemaRefs>
@@ -42008,7 +42084,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AE9A51-FA73-431C-A4D5-36C1DFA1FEFD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB7E161-F495-494F-94F7-37757C779909}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -42023,12 +42107,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>